--- a/CoursesList/Grades_PAO_II_2025_FEM.xlsx
+++ b/CoursesList/Grades_PAO_II_2025_FEM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisp\Desktop\Papers\J4 Tutor Socratico\Notas PAO II 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60801186-84E5-4105-B087-CD8D4400DFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E427DB-9CB4-4BF2-9ABF-455E1176ABCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="P3" sheetId="3" r:id="rId3"/>
     <sheet name="P4" sheetId="4" r:id="rId4"/>
     <sheet name="P5" sheetId="5" r:id="rId5"/>
-    <sheet name="P5 (2)" sheetId="6" r:id="rId6"/>
+    <sheet name="P6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="299">
   <si>
     <t>codigo</t>
   </si>
@@ -921,6 +921,12 @@
   </si>
   <si>
     <t>p06-048</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -1290,13 +1296,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6683928A-C7F0-4796-BECC-A9961919393E}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1327,8 +1333,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1359,8 +1368,12 @@
       <c r="J2">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>60.535196817516663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1391,8 +1404,12 @@
       <c r="J3">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K52" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>14.797516666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1423,8 +1440,12 @@
       <c r="J4">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>55.119294857787992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1455,8 +1476,12 @@
       <c r="J5">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>19.785604644589998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1487,8 +1512,12 @@
       <c r="J6">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>39.32350722348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1519,8 +1548,12 @@
       <c r="J7">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>64.138190388916541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1551,8 +1584,12 @@
       <c r="J8">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>65.941783105006664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1583,8 +1620,12 @@
       <c r="J9">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>72.230389233971465</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1615,8 +1656,12 @@
       <c r="J10">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>62.501165661442329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1647,8 +1692,12 @@
       <c r="J11">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>69.959740636045908</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1679,8 +1728,12 @@
       <c r="J12">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>64.532166666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1711,8 +1764,12 @@
       <c r="J13">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>35.487683333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1743,8 +1800,12 @@
       <c r="J14">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>65.221322219439998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1775,8 +1836,12 @@
       <c r="J15">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>43.046863010188765</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1807,8 +1872,12 @@
       <c r="J16">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>57.38199159880233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1839,8 +1908,12 @@
       <c r="J17">
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>60.415252103591655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1871,8 +1944,12 @@
       <c r="J18">
         <v>63</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>65.848271180127341</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1903,8 +1980,12 @@
       <c r="J19">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>26.537529838186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1935,8 +2016,12 @@
       <c r="J20">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>69.906686860181452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1967,8 +2052,12 @@
       <c r="J21">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>79.051338023730025</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1999,8 +2088,12 @@
       <c r="J22">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>70.84628676664633</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2031,8 +2124,12 @@
       <c r="J23">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>56.819984209094663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2063,8 +2160,12 @@
       <c r="J24">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>45.222698507212066</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2095,8 +2196,12 @@
       <c r="J25">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>59.209391106687988</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2127,8 +2232,12 @@
       <c r="J26">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>65.409636174359989</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2159,8 +2268,12 @@
       <c r="J27">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>51.737762148300327</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2191,8 +2304,12 @@
       <c r="J28">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>60.02006994558333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2223,8 +2340,12 @@
       <c r="J29">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>71.116935802394664</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2255,8 +2376,12 @@
       <c r="J30">
         <v>82</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>47.697375398289495</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2287,8 +2412,12 @@
       <c r="J31">
         <v>44</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>52.255968896916997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2319,8 +2448,12 @@
       <c r="J32">
         <v>54</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>68.422410644476344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2351,8 +2484,12 @@
       <c r="J33">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>38.437368190098326</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2383,8 +2520,12 @@
       <c r="J34">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>68.040917472272895</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2415,8 +2556,12 @@
       <c r="J35">
         <v>76</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>71.437484006197323</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2447,8 +2592,12 @@
       <c r="J36">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>64.850395195202665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2479,8 +2628,12 @@
       <c r="J37">
         <v>62</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>70.280073091931655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2511,8 +2664,12 @@
       <c r="J38">
         <v>61</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>76.528557330033991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2543,8 +2700,12 @@
       <c r="J39">
         <v>44</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>59.916247112562985</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2575,8 +2736,12 @@
       <c r="J40">
         <v>49</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>53.964454138980003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2607,8 +2772,12 @@
       <c r="J41">
         <v>74</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>69.541206149475002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2639,8 +2808,12 @@
       <c r="J42">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>68.642904844672202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2671,8 +2844,12 @@
       <c r="J43">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>68.031245652004657</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2703,8 +2880,12 @@
       <c r="J44">
         <v>92</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>80.537912816238318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2735,8 +2916,12 @@
       <c r="J45">
         <v>55</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>56.854286671819629</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2767,8 +2952,12 @@
       <c r="J46">
         <v>52</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>58.541259219080594</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2799,8 +2988,12 @@
       <c r="J47">
         <v>70</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>68.470817339530669</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2831,8 +3024,12 @@
       <c r="J48">
         <v>79</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>64.49882708576034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -2863,8 +3060,12 @@
       <c r="J49">
         <v>85</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>73.112573108625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2895,8 +3096,12 @@
       <c r="J50">
         <v>84</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="1">
+        <f t="shared" si="0"/>
+        <v>62.696345225236328</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2927,8 +3132,12 @@
       <c r="J51">
         <v>73</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="1">
+        <f t="shared" si="0"/>
+        <v>56.094766666666658</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2958,6 +3167,10 @@
       </c>
       <c r="J52">
         <v>83</v>
+      </c>
+      <c r="K52" s="1">
+        <f t="shared" si="0"/>
+        <v>71.608144963755336</v>
       </c>
     </row>
   </sheetData>
@@ -2968,13 +3181,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06D9429-8703-4320-B402-8BE6A17251E5}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3005,8 +3218,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -3037,8 +3253,12 @@
       <c r="J2">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>44.880566666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -3069,8 +3289,12 @@
       <c r="J3">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K43" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>61.242033333333325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3101,8 +3325,12 @@
       <c r="J4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>20.52923333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -3133,8 +3361,12 @@
       <c r="J5">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>49.736566666666661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -3165,8 +3397,12 @@
       <c r="J6">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>19.464799999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3433,12 @@
       <c r="J7">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>51.197399999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -3229,8 +3469,12 @@
       <c r="J8">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>37.052933333333328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3261,8 +3505,12 @@
       <c r="J9">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>64.725166666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3293,8 +3541,12 @@
       <c r="J10">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>62.599999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -3325,8 +3577,12 @@
       <c r="J11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>16.870066666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3357,8 +3613,12 @@
       <c r="J12">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>46.525733333333328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -3389,8 +3649,12 @@
       <c r="J13">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>61.27806666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -3421,8 +3685,12 @@
       <c r="J14">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>29.993099999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -3453,8 +3721,12 @@
       <c r="J15">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>26.971666666666664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -3485,8 +3757,12 @@
       <c r="J16">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>65.513333333333335</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -3517,8 +3793,12 @@
       <c r="J17">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>35.58626666666666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -3549,8 +3829,12 @@
       <c r="J18">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>48.214866666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -3581,8 +3865,12 @@
       <c r="J19">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>46.357933333333328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -3613,8 +3901,12 @@
       <c r="J20">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>69.188866666666655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -3645,8 +3937,12 @@
       <c r="J21">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>50.450916666666657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -3677,8 +3973,12 @@
       <c r="J22">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>51.700150000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -3709,8 +4009,12 @@
       <c r="J23">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>48.577666666666659</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -3741,8 +4045,12 @@
       <c r="J24">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>46.633266666666664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>84</v>
       </c>
@@ -3773,8 +4081,12 @@
       <c r="J25">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>47.198116666666664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -3805,8 +4117,12 @@
       <c r="J26">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>23.894333333333329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -3837,8 +4153,12 @@
       <c r="J27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>13.581466666666664</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -3869,8 +4189,12 @@
       <c r="J28">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>25.754766666666665</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>88</v>
       </c>
@@ -3901,8 +4225,12 @@
       <c r="J29">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>59.532066666666658</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -3933,8 +4261,12 @@
       <c r="J30">
         <v>51</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>59.80436666666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -3965,8 +4297,12 @@
       <c r="J31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>42.542833333333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -3997,8 +4333,12 @@
       <c r="J32">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>59.60126666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -4029,8 +4369,12 @@
       <c r="J33">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>49.428333333333327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -4061,8 +4405,12 @@
       <c r="J34">
         <v>46</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>56.29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -4093,8 +4441,12 @@
       <c r="J35">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>37.134999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -4125,8 +4477,12 @@
       <c r="J36">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>55.454716666666663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>96</v>
       </c>
@@ -4157,8 +4513,12 @@
       <c r="J37">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>43.522133333333336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
@@ -4189,8 +4549,12 @@
       <c r="J38">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>31.352266666666665</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -4221,8 +4585,12 @@
       <c r="J39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>1.948333333333333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -4253,8 +4621,12 @@
       <c r="J40">
         <v>91</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>67.214233333333326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -4285,8 +4657,12 @@
       <c r="J41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4033333333333333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -4317,8 +4693,12 @@
       <c r="J42">
         <v>61</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>60.004599999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -4349,8 +4729,12 @@
       <c r="J43">
         <v>48</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>43.982933333333328</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4360,7 +4744,7 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -4370,7 +4754,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4380,7 +4764,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4390,7 +4774,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -4448,13 +4832,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D643C4-EA4F-4806-B013-93EEAF775219}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4485,8 +4869,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -4517,8 +4904,12 @@
       <c r="J2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>9.5474999999999977</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -4549,8 +4940,12 @@
       <c r="J3">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>71.64545904517999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -4581,8 +4976,12 @@
       <c r="J4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>9.2671499999999991</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
@@ -4613,8 +5012,12 @@
       <c r="J5">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>43.145317058333326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -4645,8 +5048,12 @@
       <c r="J6">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>38.850499936708324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>108</v>
       </c>
@@ -4677,8 +5084,12 @@
       <c r="J7">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>51.877958863094996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -4709,8 +5120,12 @@
       <c r="J8">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>51.277088810638332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -4741,8 +5156,12 @@
       <c r="J9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>16.844609416426668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -4773,8 +5192,12 @@
       <c r="J10">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>35.054516666666665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -4805,8 +5228,12 @@
       <c r="J11">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>46.416407986434166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -4837,8 +5264,12 @@
       <c r="J12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>14.864999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
@@ -4869,8 +5300,12 @@
       <c r="J13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>14.303341013523333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
@@ -4901,8 +5336,12 @@
       <c r="J14">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>42.528398473219163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -4933,8 +5372,12 @@
       <c r="J15">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>65.358167211075823</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>117</v>
       </c>
@@ -4965,8 +5408,12 @@
       <c r="J16">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>31.178409330561664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -4997,8 +5444,12 @@
       <c r="J17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>2.9846499999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -5029,8 +5480,12 @@
       <c r="J18">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>68.820189999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -5061,8 +5516,12 @@
       <c r="J19">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>49.022162652437501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -5093,8 +5552,12 @@
       <c r="J20">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>48.652782396093336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>122</v>
       </c>
@@ -5125,8 +5588,12 @@
       <c r="J21">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>47.798020578049993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -5157,8 +5624,12 @@
       <c r="J22">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>42.086733333333328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -5189,8 +5660,12 @@
       <c r="J23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>3.2849999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5221,8 +5696,12 @@
       <c r="J24">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>63.246590686053338</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -5253,8 +5732,12 @@
       <c r="J25">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>44.558657298246665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -5285,8 +5768,12 @@
       <c r="J26">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>63.31672282112666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -5317,8 +5804,12 @@
       <c r="J27">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>37.302555112495</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>129</v>
       </c>
@@ -5349,8 +5840,12 @@
       <c r="J28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>1.7174999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -5381,8 +5876,12 @@
       <c r="J29">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>68.705936666666659</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -5413,8 +5912,12 @@
       <c r="J30">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>44.395349999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -5445,8 +5948,12 @@
       <c r="J31">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>39.72528158918</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -5477,8 +5984,12 @@
       <c r="J32">
         <v>43</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>57.422683333333332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>134</v>
       </c>
@@ -5509,8 +6020,12 @@
       <c r="J33">
         <v>55</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>62.065032493633332</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>135</v>
       </c>
@@ -5541,8 +6056,12 @@
       <c r="J34">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>53.910223042505002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>136</v>
       </c>
@@ -5573,8 +6092,12 @@
       <c r="J35">
         <v>77</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>75.564673333333332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -5605,8 +6128,12 @@
       <c r="J36">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>60.152839999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -5637,8 +6164,12 @@
       <c r="J37">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>16.606311456733334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>139</v>
       </c>
@@ -5669,8 +6200,12 @@
       <c r="J38">
         <v>29</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>49.199886352385832</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -5701,8 +6236,12 @@
       <c r="J39">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>41.14613587817999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>141</v>
       </c>
@@ -5733,8 +6272,12 @@
       <c r="J40">
         <v>12</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>29.912213478325832</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -5765,8 +6308,12 @@
       <c r="J41">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>51.458681404008331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -5797,8 +6344,12 @@
       <c r="J42">
         <v>27</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>33.317552604883332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -5829,8 +6380,12 @@
       <c r="J43">
         <v>55</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>68.018712568516662</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -5861,8 +6416,12 @@
       <c r="J44">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>30.335816666666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -5893,8 +6452,12 @@
       <c r="J45">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>43.512636639874998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -5925,8 +6488,12 @@
       <c r="J46">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>50.160296666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -5957,8 +6524,12 @@
       <c r="J47">
         <v>38</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>30.922534937441668</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -5989,8 +6560,12 @@
       <c r="J48">
         <v>23</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>28.16709679736833</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -6021,8 +6596,12 @@
       <c r="J49">
         <v>56</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>49.212278001343336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -6032,7 +6611,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -6042,7 +6621,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -6060,13 +6639,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50D314B-C5D2-4604-9044-09199DFEB247}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6097,8 +6676,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -6129,8 +6711,12 @@
       <c r="J2">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>64.533683333333329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -6161,8 +6747,12 @@
       <c r="J3">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>66.032466666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -6193,8 +6783,12 @@
       <c r="J4">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>53.872583333333338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -6225,8 +6819,12 @@
       <c r="J5">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>46.280966666666664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>155</v>
       </c>
@@ -6257,8 +6855,12 @@
       <c r="J6">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>50.291466666666658</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>156</v>
       </c>
@@ -6289,8 +6891,12 @@
       <c r="J7">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>30.002133333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>157</v>
       </c>
@@ -6321,8 +6927,12 @@
       <c r="J8">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>60.406850000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -6353,8 +6963,12 @@
       <c r="J9">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>43.703566666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -6385,8 +6999,12 @@
       <c r="J10">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>68.47733333333332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>160</v>
       </c>
@@ -6417,8 +7035,12 @@
       <c r="J11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>53.052549999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -6449,8 +7071,12 @@
       <c r="J12">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>50.630233333333329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -6481,8 +7107,12 @@
       <c r="J13">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>52.602699999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>163</v>
       </c>
@@ -6513,8 +7143,12 @@
       <c r="J14">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>64.101849999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -6545,8 +7179,12 @@
       <c r="J15">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>62.903649999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -6577,8 +7215,12 @@
       <c r="J16">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>56.044533333333327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -6609,8 +7251,12 @@
       <c r="J17">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>48.1173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>167</v>
       </c>
@@ -6641,8 +7287,12 @@
       <c r="J18">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>38.19166666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -6673,8 +7323,12 @@
       <c r="J19">
         <v>74</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>66.008099999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -6705,8 +7359,12 @@
       <c r="J20">
         <v>70</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>57.995233333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -6737,8 +7395,12 @@
       <c r="J21">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>62.324816666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>171</v>
       </c>
@@ -6769,8 +7431,12 @@
       <c r="J22">
         <v>53</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>54.010216666666665</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -6801,8 +7467,12 @@
       <c r="J23">
         <v>55</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>56.543500000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>173</v>
       </c>
@@ -6833,8 +7503,12 @@
       <c r="J24">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>58.930583333333331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>174</v>
       </c>
@@ -6865,8 +7539,12 @@
       <c r="J25">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>57.394483333333326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>175</v>
       </c>
@@ -6897,8 +7575,12 @@
       <c r="J26">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>67.491299999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>176</v>
       </c>
@@ -6929,8 +7611,12 @@
       <c r="J27">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>60.25031666666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>177</v>
       </c>
@@ -6961,8 +7647,12 @@
       <c r="J28">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>46.34726666666667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>178</v>
       </c>
@@ -6993,8 +7683,12 @@
       <c r="J29">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>58.19404999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>179</v>
       </c>
@@ -7025,8 +7719,12 @@
       <c r="J30">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>64.661466666666655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>180</v>
       </c>
@@ -7057,8 +7755,12 @@
       <c r="J31">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>52.051666666666662</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>181</v>
       </c>
@@ -7089,8 +7791,12 @@
       <c r="J32">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>59.995366666666662</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>182</v>
       </c>
@@ -7121,8 +7827,12 @@
       <c r="J33">
         <v>47</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>51.900233333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -7153,8 +7863,12 @@
       <c r="J34">
         <v>58</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>64.709733333333332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>184</v>
       </c>
@@ -7185,8 +7899,12 @@
       <c r="J35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>49.809149999999988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -7217,8 +7935,12 @@
       <c r="J36">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>54.130733333333332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>186</v>
       </c>
@@ -7249,8 +7971,12 @@
       <c r="J37">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>28.58583333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -7281,8 +8007,12 @@
       <c r="J38">
         <v>53</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>65.248249999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>188</v>
       </c>
@@ -7313,8 +8043,12 @@
       <c r="J39">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>55.738566666666664</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>189</v>
       </c>
@@ -7345,8 +8079,12 @@
       <c r="J40">
         <v>43</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>47.9315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -7377,8 +8115,12 @@
       <c r="J41">
         <v>56</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>69.084983333333327</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -7409,8 +8151,12 @@
       <c r="J42">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>45.500733333333329</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>192</v>
       </c>
@@ -7441,8 +8187,12 @@
       <c r="J43">
         <v>58</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>56.800550000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>193</v>
       </c>
@@ -7473,8 +8223,12 @@
       <c r="J44">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>28.956233333333326</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -7505,8 +8259,12 @@
       <c r="J45">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>56.238099999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -7537,8 +8295,12 @@
       <c r="J46">
         <v>81</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>67.871733333333339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -7569,8 +8331,12 @@
       <c r="J47">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>52.232499999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -7601,8 +8367,12 @@
       <c r="J48">
         <v>34</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>51.130166666666653</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -7633,8 +8403,12 @@
       <c r="J49">
         <v>44</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>45.789899999999989</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>199</v>
       </c>
@@ -7665,8 +8439,12 @@
       <c r="J50">
         <v>54</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="1">
+        <f t="shared" si="0"/>
+        <v>50.569066666666657</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>200</v>
       </c>
@@ -7697,8 +8475,12 @@
       <c r="J51">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="1">
+        <f t="shared" si="0"/>
+        <v>74.679266666666649</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -7716,13 +8498,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A4A384-9885-48EF-9409-BDD8E2A0903E}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7753,8 +8535,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>201</v>
       </c>
@@ -7785,8 +8570,12 @@
       <c r="J2">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>76.579070073994998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -7817,8 +8606,12 @@
       <c r="J3">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>63.404541254933328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>203</v>
       </c>
@@ -7849,8 +8642,12 @@
       <c r="J4">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>61.52176262326666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>204</v>
       </c>
@@ -7881,8 +8678,12 @@
       <c r="J5">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>66.793837080889176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>205</v>
       </c>
@@ -7913,8 +8714,12 @@
       <c r="J6">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>9.3271999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>206</v>
       </c>
@@ -7945,8 +8750,12 @@
       <c r="J7">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>58.888716345459997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -7977,8 +8786,12 @@
       <c r="J8">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>60.980756202403327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>208</v>
       </c>
@@ -8009,8 +8822,12 @@
       <c r="J9">
         <v>62</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>55.198283885298324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -8041,8 +8858,12 @@
       <c r="J10">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>62.26417829261333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>210</v>
       </c>
@@ -8073,8 +8894,12 @@
       <c r="J11">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>66.657683094203335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>211</v>
       </c>
@@ -8105,8 +8930,12 @@
       <c r="J12">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>60.876748926398328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>212</v>
       </c>
@@ -8137,8 +8966,12 @@
       <c r="J13">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>60.462232564366666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>213</v>
       </c>
@@ -8169,8 +9002,12 @@
       <c r="J14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4849999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>214</v>
       </c>
@@ -8201,8 +9038,12 @@
       <c r="J15">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>59.955459864959998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>215</v>
       </c>
@@ -8233,8 +9074,12 @@
       <c r="J16">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>33.992139220133325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>216</v>
       </c>
@@ -8265,8 +9110,12 @@
       <c r="J17">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>44.675791205949999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>217</v>
       </c>
@@ -8297,8 +9146,12 @@
       <c r="J18">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>69.06566391556666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>218</v>
       </c>
@@ -8329,8 +9182,12 @@
       <c r="J19">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>74.169565471903326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>219</v>
       </c>
@@ -8361,8 +9218,12 @@
       <c r="J20">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>14.942916666666665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>220</v>
       </c>
@@ -8393,8 +9254,12 @@
       <c r="J21">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>67.034976895301668</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>221</v>
       </c>
@@ -8425,8 +9290,12 @@
       <c r="J22">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>73.195284515991673</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>222</v>
       </c>
@@ -8457,8 +9326,12 @@
       <c r="J23">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>64.513571778680003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -8489,8 +9362,12 @@
       <c r="J24">
         <v>58</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>53.75608715705166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>224</v>
       </c>
@@ -8521,8 +9398,12 @@
       <c r="J25">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>70.141581969678327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>225</v>
       </c>
@@ -8553,8 +9434,12 @@
       <c r="J26">
         <v>61</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>58.083308225068336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>226</v>
       </c>
@@ -8585,8 +9470,12 @@
       <c r="J27">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>66.747009125708331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>227</v>
       </c>
@@ -8617,8 +9506,12 @@
       <c r="J28">
         <v>64</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>71.259889265369992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>228</v>
       </c>
@@ -8649,8 +9542,12 @@
       <c r="J29">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>50.197038947773336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>229</v>
       </c>
@@ -8681,8 +9578,12 @@
       <c r="J30">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>73.072197889269987</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>230</v>
       </c>
@@ -8713,8 +9614,12 @@
       <c r="J31">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>60.097547415688325</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>231</v>
       </c>
@@ -8745,8 +9650,12 @@
       <c r="J32">
         <v>84</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>83.48595029668833</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>232</v>
       </c>
@@ -8777,8 +9686,12 @@
       <c r="J33">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>70.633730350995833</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>233</v>
       </c>
@@ -8809,8 +9722,12 @@
       <c r="J34">
         <v>70</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>76.30224899289999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>234</v>
       </c>
@@ -8841,8 +9758,12 @@
       <c r="J35">
         <v>58</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>56.827339674368325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -8873,8 +9794,12 @@
       <c r="J36">
         <v>78</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>60.888489267786667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>236</v>
       </c>
@@ -8905,8 +9830,12 @@
       <c r="J37">
         <v>56</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>64.088011996878336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>237</v>
       </c>
@@ -8937,8 +9866,12 @@
       <c r="J38">
         <v>89</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>74.530655321306668</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>238</v>
       </c>
@@ -8969,8 +9902,12 @@
       <c r="J39">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>58.706249999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -9001,8 +9938,12 @@
       <c r="J40">
         <v>56</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>54.62211277243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -9033,8 +9974,12 @@
       <c r="J41">
         <v>58</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>54.290859018428328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>241</v>
       </c>
@@ -9065,8 +10010,12 @@
       <c r="J42">
         <v>74</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>68.774214628549998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>242</v>
       </c>
@@ -9097,8 +10046,12 @@
       <c r="J43">
         <v>56</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>53.513940814110001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>243</v>
       </c>
@@ -9129,8 +10082,12 @@
       <c r="J44">
         <v>65</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>57.741432120989998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>244</v>
       </c>
@@ -9161,8 +10118,12 @@
       <c r="J45">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>52.316441059088334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>245</v>
       </c>
@@ -9193,8 +10154,12 @@
       <c r="J46">
         <v>67</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>70.348171025406657</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>246</v>
       </c>
@@ -9225,8 +10190,12 @@
       <c r="J47">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>53.123703068056663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -9257,8 +10226,12 @@
       <c r="J48">
         <v>60</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>62.109005669878329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>248</v>
       </c>
@@ -9289,8 +10262,12 @@
       <c r="J49">
         <v>9</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>14.701216419733329</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -9300,7 +10277,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -9310,7 +10287,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -9328,13 +10305,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4309DD8B-C3AE-490A-BFD6-B77DAC7DA4EB}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9365,8 +10342,11 @@
       <c r="J1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>249</v>
       </c>
@@ -9397,8 +10377,12 @@
       <c r="J2">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1">
+        <f>(0.3*J2)+((E2+I2)*0.35)</f>
+        <v>69.471296454184994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>250</v>
       </c>
@@ -9429,8 +10413,12 @@
       <c r="J3">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <v>44.614382153079994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>251</v>
       </c>
@@ -9461,8 +10449,12 @@
       <c r="J4">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>63.298644614179992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>252</v>
       </c>
@@ -9493,8 +10485,12 @@
       <c r="J5">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>63.455141060433327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>253</v>
       </c>
@@ -9525,8 +10521,12 @@
       <c r="J6">
         <v>86</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>66.846465981768333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>254</v>
       </c>
@@ -9557,8 +10557,12 @@
       <c r="J7">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>61.747031504999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>255</v>
       </c>
@@ -9589,8 +10593,12 @@
       <c r="J8">
         <v>86</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>73.407575338726659</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>256</v>
       </c>
@@ -9621,8 +10629,12 @@
       <c r="J9">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>72.489166666666662</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -9653,8 +10665,12 @@
       <c r="J10">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>53.131503680999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -9685,8 +10701,12 @@
       <c r="J11">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>84.431739069226666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -9717,8 +10737,12 @@
       <c r="J12">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>56.893700434426663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>260</v>
       </c>
@@ -9749,8 +10773,12 @@
       <c r="J13">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>76.665935129108334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>261</v>
       </c>
@@ -9781,8 +10809,12 @@
       <c r="J14">
         <v>96</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>75.915630239439992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -9813,8 +10845,12 @@
       <c r="J15">
         <v>62</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>60.039999999999992</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -9845,8 +10881,12 @@
       <c r="J16">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>50.26422162980667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>264</v>
       </c>
@@ -9877,8 +10917,12 @@
       <c r="J17">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>61.42795485705733</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -9909,8 +10953,12 @@
       <c r="J18">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>52.59426095968</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -9941,8 +10989,12 @@
       <c r="J19">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>46.527383333333333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -9973,8 +11025,12 @@
       <c r="J20">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>77.399478588846648</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -10005,8 +11061,12 @@
       <c r="J21">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>74.083333333333329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>269</v>
       </c>
@@ -10037,8 +11097,12 @@
       <c r="J22">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>62.898559555489996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -10069,8 +11133,12 @@
       <c r="J23">
         <v>88</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>68.382735392698336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>271</v>
       </c>
@@ -10101,8 +11169,12 @@
       <c r="J24">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>63.771232847416655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -10133,8 +11205,12 @@
       <c r="J25">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>57.987718325576665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -10165,8 +11241,12 @@
       <c r="J26">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>69.021035989673322</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -10197,8 +11277,12 @@
       <c r="J27">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>69.1273022524</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -10229,8 +11313,12 @@
       <c r="J28">
         <v>81</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>67.46846563799933</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -10261,8 +11349,12 @@
       <c r="J29">
         <v>71</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>62.031331927883329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -10293,8 +11385,12 @@
       <c r="J30">
         <v>64</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>64.961596857549992</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -10325,8 +11421,12 @@
       <c r="J31">
         <v>42</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>39.211666666666666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -10357,8 +11457,12 @@
       <c r="J32">
         <v>58</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>66.665020470656657</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>280</v>
       </c>
@@ -10389,8 +11493,12 @@
       <c r="J33">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>39.18532478978333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>281</v>
       </c>
@@ -10421,8 +11529,12 @@
       <c r="J34">
         <v>69</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>58.024634274013323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -10453,8 +11565,12 @@
       <c r="J35">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>64.787983109516659</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -10485,8 +11601,12 @@
       <c r="J36">
         <v>61</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>63.310324086268338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>284</v>
       </c>
@@ -10517,8 +11637,12 @@
       <c r="J37">
         <v>38</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>32.347499999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>285</v>
       </c>
@@ -10549,8 +11673,12 @@
       <c r="J38">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>70.296250000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>286</v>
       </c>
@@ -10581,8 +11709,12 @@
       <c r="J39">
         <v>75</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>54.822018460479995</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -10613,8 +11745,12 @@
       <c r="J40">
         <v>89</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>65.835949999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>288</v>
       </c>
@@ -10645,8 +11781,12 @@
       <c r="J41">
         <v>47</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>51.036022746279997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>289</v>
       </c>
@@ -10677,8 +11817,12 @@
       <c r="J42">
         <v>57</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>55.60833011199999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>290</v>
       </c>
@@ -10709,8 +11853,12 @@
       <c r="J43">
         <v>74</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>69.943669462813332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -10741,8 +11889,12 @@
       <c r="J44">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>51.926743758501658</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>292</v>
       </c>
@@ -10773,8 +11925,12 @@
       <c r="J45">
         <v>81</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>74.315787171233339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -10805,8 +11961,12 @@
       <c r="J46">
         <v>85</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>83.584363750816664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -10837,8 +11997,12 @@
       <c r="J47">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>28.742387461924999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>295</v>
       </c>
@@ -10869,8 +12033,12 @@
       <c r="J48">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>37.732315025376664</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -10901,8 +12069,12 @@
       <c r="J49">
         <v>57</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>58.365339994759992</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -10912,7 +12084,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -10922,7 +12094,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>

--- a/CoursesList/Grades_PAO_II_2025_FEM.xlsx
+++ b/CoursesList/Grades_PAO_II_2025_FEM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisp\Desktop\Papers\J4 Tutor Socratico\Notas PAO II 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E427DB-9CB4-4BF2-9ABF-455E1176ABCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF018A8-B20C-4108-80F4-4274E32688EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="301">
   <si>
     <t>codigo</t>
   </si>
@@ -927,6 +927,12 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>tercer examen</t>
+  </si>
+  <si>
+    <t>FINAL CON 3er Examen</t>
   </si>
 </sst>
 </file>
@@ -986,7 +992,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1296,13 +1314,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6683928A-C7F0-4796-BECC-A9961919393E}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1336,8 +1354,14 @@
       <c r="K1" s="2" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1372,8 +1396,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>60.535196817516663</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>75</v>
+      </c>
+      <c r="M2" s="1">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1438,14 @@
         <f t="shared" ref="K3:K52" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>14.797516666666667</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1444,8 +1480,14 @@
         <f t="shared" si="0"/>
         <v>55.119294857787992</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>42</v>
+      </c>
+      <c r="M4" s="1">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1480,8 +1522,14 @@
         <f t="shared" si="0"/>
         <v>19.785604644589998</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1516,8 +1564,14 @@
         <f t="shared" si="0"/>
         <v>39.32350722348</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>39.349999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1552,8 +1606,14 @@
         <f t="shared" si="0"/>
         <v>64.138190388916541</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>64.699999999999989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1588,8 +1648,14 @@
         <f t="shared" si="0"/>
         <v>65.941783105006664</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1624,8 +1690,14 @@
         <f t="shared" si="0"/>
         <v>72.230389233971465</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1660,8 +1732,14 @@
         <f t="shared" si="0"/>
         <v>62.501165661442329</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>62.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1696,8 +1774,14 @@
         <f t="shared" si="0"/>
         <v>69.959740636045908</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1732,8 +1816,14 @@
         <f t="shared" si="0"/>
         <v>64.532166666666669</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1768,8 +1858,14 @@
         <f t="shared" si="0"/>
         <v>35.487683333333337</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>35.450000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1804,8 +1900,14 @@
         <f t="shared" si="0"/>
         <v>65.221322219439998</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>65.349999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1840,8 +1942,14 @@
         <f t="shared" si="0"/>
         <v>43.046863010188765</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1876,8 +1984,14 @@
         <f t="shared" si="0"/>
         <v>57.38199159880233</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>47</v>
+      </c>
+      <c r="M16" s="1">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1912,8 +2026,14 @@
         <f t="shared" si="0"/>
         <v>60.415252103591655</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1948,8 +2068,14 @@
         <f t="shared" si="0"/>
         <v>65.848271180127341</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>66.150000000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1984,8 +2110,14 @@
         <f t="shared" si="0"/>
         <v>26.537529838186</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>25.049999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2020,8 +2152,14 @@
         <f t="shared" si="0"/>
         <v>69.906686860181452</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>70.199999999999989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2056,8 +2194,14 @@
         <f t="shared" si="0"/>
         <v>79.051338023730025</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>87</v>
+      </c>
+      <c r="M21" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2092,8 +2236,14 @@
         <f t="shared" si="0"/>
         <v>70.84628676664633</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2128,8 +2278,14 @@
         <f t="shared" si="0"/>
         <v>56.819984209094663</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>60</v>
+      </c>
+      <c r="M23" s="1">
+        <v>58.249999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2164,8 +2320,14 @@
         <f t="shared" si="0"/>
         <v>45.222698507212066</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>42</v>
+      </c>
+      <c r="M24" s="1">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2200,8 +2362,14 @@
         <f t="shared" si="0"/>
         <v>59.209391106687988</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>41</v>
+      </c>
+      <c r="M25" s="1">
+        <v>53.349999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2236,8 +2404,14 @@
         <f t="shared" si="0"/>
         <v>65.409636174359989</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2272,8 +2446,14 @@
         <f t="shared" si="0"/>
         <v>51.737762148300327</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>66</v>
+      </c>
+      <c r="M27" s="1">
+        <v>55.55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2308,8 +2488,14 @@
         <f t="shared" si="0"/>
         <v>60.02006994558333</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>60.349999999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2344,8 +2530,14 @@
         <f t="shared" si="0"/>
         <v>71.116935802394664</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2380,8 +2572,14 @@
         <f t="shared" si="0"/>
         <v>47.697375398289495</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>31</v>
+      </c>
+      <c r="M30" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2416,8 +2614,14 @@
         <f t="shared" si="0"/>
         <v>52.255968896916997</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>51</v>
+      </c>
+      <c r="M31" s="1">
+        <v>52.399999999999991</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2452,8 +2656,14 @@
         <f t="shared" si="0"/>
         <v>68.422410644476344</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2488,8 +2698,14 @@
         <f t="shared" si="0"/>
         <v>38.437368190098326</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>36.349999999999994</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2524,8 +2740,14 @@
         <f t="shared" si="0"/>
         <v>68.040917472272895</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2560,8 +2782,14 @@
         <f t="shared" si="0"/>
         <v>71.437484006197323</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2596,8 +2824,14 @@
         <f t="shared" si="0"/>
         <v>64.850395195202665</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2632,8 +2866,14 @@
         <f t="shared" si="0"/>
         <v>70.280073091931655</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>70.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2668,8 +2908,14 @@
         <f t="shared" si="0"/>
         <v>76.528557330033991</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>76.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2704,8 +2950,14 @@
         <f t="shared" si="0"/>
         <v>59.916247112562985</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>60.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2740,8 +2992,14 @@
         <f t="shared" si="0"/>
         <v>53.964454138980003</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40">
+        <v>61</v>
+      </c>
+      <c r="M40" s="1">
+        <v>56.349999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2776,8 +3034,14 @@
         <f t="shared" si="0"/>
         <v>69.541206149475002</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2812,8 +3076,14 @@
         <f t="shared" si="0"/>
         <v>68.642904844672202</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>68.949999999999989</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2848,8 +3118,14 @@
         <f t="shared" si="0"/>
         <v>68.031245652004657</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>68.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2884,8 +3160,14 @@
         <f t="shared" si="0"/>
         <v>80.537912816238318</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>81.149999999999991</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2920,8 +3202,14 @@
         <f t="shared" si="0"/>
         <v>56.854286671819629</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45">
+        <v>43</v>
+      </c>
+      <c r="M45" s="1">
+        <v>52.55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2956,8 +3244,14 @@
         <f t="shared" si="0"/>
         <v>58.541259219080594</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46">
+        <v>64.27000000000001</v>
+      </c>
+      <c r="M46" s="1">
+        <v>60.144500000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2992,8 +3286,14 @@
         <f t="shared" si="0"/>
         <v>68.470817339530669</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -3028,8 +3328,14 @@
         <f t="shared" si="0"/>
         <v>64.49882708576034</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>64.649999999999991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -3064,8 +3370,14 @@
         <f t="shared" si="0"/>
         <v>73.112573108625</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49">
+        <v>67</v>
+      </c>
+      <c r="M49" s="1">
+        <v>73.449999999999989</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -3100,8 +3412,14 @@
         <f t="shared" si="0"/>
         <v>62.696345225236328</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -3136,8 +3454,14 @@
         <f t="shared" si="0"/>
         <v>56.094766666666658</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51">
+        <v>41</v>
+      </c>
+      <c r="M51" s="1">
+        <v>56.199999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -3171,6 +3495,12 @@
       <c r="K52" s="1">
         <f t="shared" si="0"/>
         <v>71.608144963755336</v>
+      </c>
+      <c r="L52">
+        <v>54</v>
+      </c>
+      <c r="M52" s="1">
+        <v>67.25</v>
       </c>
     </row>
   </sheetData>
@@ -3181,13 +3511,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06D9429-8703-4320-B402-8BE6A17251E5}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3221,8 +3551,14 @@
       <c r="K1" s="2" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -3257,8 +3593,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>44.880566666666667</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>40.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -3293,8 +3635,14 @@
         <f t="shared" ref="K3:K43" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>61.242033333333325</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>61.749999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3329,8 +3677,14 @@
         <f t="shared" si="0"/>
         <v>20.52923333333333</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>20.549999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -3365,8 +3719,14 @@
         <f t="shared" si="0"/>
         <v>49.736566666666661</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>43.349999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -3401,8 +3761,14 @@
         <f t="shared" si="0"/>
         <v>19.464799999999997</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -3437,8 +3803,14 @@
         <f t="shared" si="0"/>
         <v>51.197399999999995</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>18</v>
+      </c>
+      <c r="M7">
+        <v>51.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -3473,8 +3845,14 @@
         <f t="shared" si="0"/>
         <v>37.052933333333328</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>37.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3509,8 +3887,14 @@
         <f t="shared" si="0"/>
         <v>64.725166666666667</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>64.849999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3545,8 +3929,14 @@
         <f t="shared" si="0"/>
         <v>62.599999999999994</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>62.949999999999989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -3581,8 +3971,14 @@
         <f t="shared" si="0"/>
         <v>16.870066666666666</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>16.849999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3617,8 +4013,14 @@
         <f t="shared" si="0"/>
         <v>46.525733333333328</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>39.199999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -3653,8 +4055,14 @@
         <f t="shared" si="0"/>
         <v>61.27806666666666</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>61.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -3689,8 +4097,14 @@
         <f t="shared" si="0"/>
         <v>29.993099999999998</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -3725,8 +4139,14 @@
         <f t="shared" si="0"/>
         <v>26.971666666666664</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -3761,8 +4181,14 @@
         <f t="shared" si="0"/>
         <v>65.513333333333335</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>66.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -3797,8 +4223,14 @@
         <f t="shared" si="0"/>
         <v>35.58626666666666</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>35.449999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -3833,8 +4265,14 @@
         <f t="shared" si="0"/>
         <v>48.214866666666666</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1">
+        <v>13</v>
+      </c>
+      <c r="M18">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -3869,8 +4307,14 @@
         <f t="shared" si="0"/>
         <v>46.357933333333328</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1">
+        <v>13</v>
+      </c>
+      <c r="M19">
+        <v>45.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -3905,8 +4349,14 @@
         <f t="shared" si="0"/>
         <v>69.188866666666655</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1">
+        <v>12</v>
+      </c>
+      <c r="M20">
+        <v>65.399999999999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -3941,8 +4391,14 @@
         <f t="shared" si="0"/>
         <v>50.450916666666657</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>43.699999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -3977,8 +4433,14 @@
         <f t="shared" si="0"/>
         <v>51.700150000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>50.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -4013,8 +4475,14 @@
         <f t="shared" si="0"/>
         <v>48.577666666666659</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>41.999999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4049,8 +4517,14 @@
         <f t="shared" si="0"/>
         <v>46.633266666666664</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>84</v>
       </c>
@@ -4085,8 +4559,14 @@
         <f t="shared" si="0"/>
         <v>47.198116666666664</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>42.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -4121,8 +4601,14 @@
         <f t="shared" si="0"/>
         <v>23.894333333333329</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>23.849999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -4157,8 +4643,14 @@
         <f t="shared" si="0"/>
         <v>13.581466666666664</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -4193,8 +4685,14 @@
         <f t="shared" si="0"/>
         <v>25.754766666666665</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>25.999999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>88</v>
       </c>
@@ -4229,8 +4727,14 @@
         <f t="shared" si="0"/>
         <v>59.532066666666658</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>60.099999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -4265,8 +4769,14 @@
         <f t="shared" si="0"/>
         <v>59.80436666666666</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>60.099999999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -4301,8 +4811,14 @@
         <f t="shared" si="0"/>
         <v>42.542833333333334</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -4337,8 +4853,14 @@
         <f t="shared" si="0"/>
         <v>59.60126666666666</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>60.199999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -4373,8 +4895,14 @@
         <f t="shared" si="0"/>
         <v>49.428333333333327</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="1">
+        <v>14</v>
+      </c>
+      <c r="M33">
+        <v>49.649999999999991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -4409,8 +4937,14 @@
         <f t="shared" si="0"/>
         <v>56.29</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>37</v>
+      </c>
+      <c r="M34">
+        <v>63.499999999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -4445,8 +4979,14 @@
         <f t="shared" si="0"/>
         <v>37.134999999999998</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -4481,8 +5021,14 @@
         <f t="shared" si="0"/>
         <v>55.454716666666663</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="1">
+        <v>20</v>
+      </c>
+      <c r="M36">
+        <v>54.349999999999994</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>96</v>
       </c>
@@ -4517,8 +5063,14 @@
         <f t="shared" si="0"/>
         <v>43.522133333333336</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>39.099999999999994</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
@@ -4553,8 +5105,14 @@
         <f t="shared" si="0"/>
         <v>31.352266666666665</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -4589,8 +5147,14 @@
         <f t="shared" si="0"/>
         <v>1.948333333333333</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>2.0999999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -4625,8 +5189,14 @@
         <f t="shared" si="0"/>
         <v>67.214233333333326</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>67.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -4661,8 +5231,14 @@
         <f t="shared" si="0"/>
         <v>2.4033333333333333</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>2.4499999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -4697,8 +5273,14 @@
         <f t="shared" si="0"/>
         <v>60.004599999999996</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -4733,8 +5315,14 @@
         <f t="shared" si="0"/>
         <v>43.982933333333328</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>44.149999999999991</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4744,7 +5332,7 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -4754,7 +5342,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4764,7 +5352,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4774,7 +5362,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -4832,13 +5420,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D643C4-EA4F-4806-B013-93EEAF775219}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4872,8 +5460,14 @@
       <c r="K1" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -4908,8 +5502,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>9.5474999999999977</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>9.5999999999999979</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -4944,8 +5544,14 @@
         <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>71.64545904517999</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>72.150000000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -4980,8 +5586,14 @@
         <f t="shared" si="0"/>
         <v>9.2671499999999991</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>9.2499999999999982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
@@ -5016,8 +5628,14 @@
         <f t="shared" si="0"/>
         <v>43.145317058333326</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -5052,8 +5670,14 @@
         <f t="shared" si="0"/>
         <v>38.850499936708324</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>35.199999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>108</v>
       </c>
@@ -5088,8 +5712,14 @@
         <f t="shared" si="0"/>
         <v>51.877958863094996</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>57.699999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -5124,8 +5754,14 @@
         <f t="shared" si="0"/>
         <v>51.277088810638332</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>55.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5160,8 +5796,14 @@
         <f t="shared" si="0"/>
         <v>16.844609416426668</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -5196,8 +5838,14 @@
         <f t="shared" si="0"/>
         <v>35.054516666666665</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>33.099999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -5232,8 +5880,14 @@
         <f t="shared" si="0"/>
         <v>46.416407986434166</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -5268,8 +5922,14 @@
         <f t="shared" si="0"/>
         <v>14.864999999999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
@@ -5304,8 +5964,14 @@
         <f t="shared" si="0"/>
         <v>14.303341013523333</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
@@ -5340,8 +6006,14 @@
         <f t="shared" si="0"/>
         <v>42.528398473219163</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>35.699999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -5376,8 +6048,14 @@
         <f t="shared" si="0"/>
         <v>65.358167211075823</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>65.849999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>117</v>
       </c>
@@ -5412,8 +6090,14 @@
         <f t="shared" si="0"/>
         <v>31.178409330561664</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>29.449999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -5448,8 +6132,14 @@
         <f t="shared" si="0"/>
         <v>2.9846499999999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -5484,8 +6174,14 @@
         <f t="shared" si="0"/>
         <v>68.820189999999997</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1">
+        <v>25</v>
+      </c>
+      <c r="M18">
+        <v>68.349999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -5520,8 +6216,14 @@
         <f t="shared" si="0"/>
         <v>49.022162652437501</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>48.349999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -5556,8 +6258,14 @@
         <f t="shared" si="0"/>
         <v>48.652782396093336</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1">
+        <v>13</v>
+      </c>
+      <c r="M20">
+        <v>47.65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>122</v>
       </c>
@@ -5592,8 +6300,14 @@
         <f t="shared" si="0"/>
         <v>47.798020578049993</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -5628,8 +6342,14 @@
         <f t="shared" si="0"/>
         <v>42.086733333333328</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>38.449999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -5664,8 +6384,14 @@
         <f t="shared" si="0"/>
         <v>3.2849999999999997</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5700,8 +6426,14 @@
         <f t="shared" si="0"/>
         <v>63.246590686053338</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>64.599999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -5736,8 +6468,14 @@
         <f t="shared" si="0"/>
         <v>44.558657298246665</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>41.849999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -5772,8 +6510,14 @@
         <f t="shared" si="0"/>
         <v>63.31672282112666</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>63.649999999999991</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -5808,8 +6552,14 @@
         <f t="shared" si="0"/>
         <v>37.302555112495</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>129</v>
       </c>
@@ -5844,8 +6594,14 @@
         <f t="shared" si="0"/>
         <v>1.7174999999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -5880,8 +6636,14 @@
         <f t="shared" si="0"/>
         <v>68.705936666666659</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>72.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -5916,8 +6678,14 @@
         <f t="shared" si="0"/>
         <v>44.395349999999993</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>35.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -5952,8 +6720,14 @@
         <f t="shared" si="0"/>
         <v>39.72528158918</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31">
+        <v>37.549999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -5988,8 +6762,14 @@
         <f t="shared" si="0"/>
         <v>57.422683333333332</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="1">
+        <v>7</v>
+      </c>
+      <c r="M32">
+        <v>51.749999999999993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>134</v>
       </c>
@@ -6024,8 +6804,14 @@
         <f t="shared" si="0"/>
         <v>62.065032493633332</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="1">
+        <v>20</v>
+      </c>
+      <c r="M33">
+        <v>61.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>135</v>
       </c>
@@ -6060,8 +6846,14 @@
         <f t="shared" si="0"/>
         <v>53.910223042505002</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>4</v>
+      </c>
+      <c r="M34">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>136</v>
       </c>
@@ -6096,8 +6888,14 @@
         <f t="shared" si="0"/>
         <v>75.564673333333332</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>75.949999999999989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -6132,8 +6930,14 @@
         <f t="shared" si="0"/>
         <v>60.152839999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -6168,8 +6972,14 @@
         <f t="shared" si="0"/>
         <v>16.606311456733334</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>15.249999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>139</v>
       </c>
@@ -6204,8 +7014,14 @@
         <f t="shared" si="0"/>
         <v>49.199886352385832</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -6240,8 +7056,14 @@
         <f t="shared" si="0"/>
         <v>41.14613587817999</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>37.599999999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>141</v>
       </c>
@@ -6276,8 +7098,14 @@
         <f t="shared" si="0"/>
         <v>29.912213478325832</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>26.699999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -6312,8 +7140,14 @@
         <f t="shared" si="0"/>
         <v>51.458681404008331</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="1">
+        <v>10</v>
+      </c>
+      <c r="M41">
+        <v>52.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -6348,8 +7182,14 @@
         <f t="shared" si="0"/>
         <v>33.317552604883332</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="1">
+        <v>4</v>
+      </c>
+      <c r="M42">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -6384,8 +7224,14 @@
         <f t="shared" si="0"/>
         <v>68.018712568516662</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="1">
+        <v>34</v>
+      </c>
+      <c r="M43">
+        <v>73.199999999999989</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -6420,8 +7266,14 @@
         <f t="shared" si="0"/>
         <v>30.335816666666666</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -6456,8 +7308,14 @@
         <f t="shared" si="0"/>
         <v>43.512636639874998</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>35.15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -6492,8 +7350,14 @@
         <f t="shared" si="0"/>
         <v>50.160296666666667</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="1">
+        <v>7</v>
+      </c>
+      <c r="M46">
+        <v>46.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -6528,8 +7392,14 @@
         <f t="shared" si="0"/>
         <v>30.922534937441668</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>29.949999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -6564,8 +7434,14 @@
         <f t="shared" si="0"/>
         <v>28.16709679736833</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="1">
+        <v>7</v>
+      </c>
+      <c r="M48">
+        <v>26.849999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -6600,8 +7476,14 @@
         <f t="shared" si="0"/>
         <v>49.212278001343336</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="1">
+        <v>8</v>
+      </c>
+      <c r="M49">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -6611,7 +7493,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -6621,7 +7503,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -6639,13 +7521,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50D314B-C5D2-4604-9044-09199DFEB247}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6679,8 +7561,14 @@
       <c r="K1" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -6715,8 +7603,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>64.533683333333329</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>33</v>
+      </c>
+      <c r="M2" s="1">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -6751,8 +7645,14 @@
         <f t="shared" ref="K3:K51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>66.032466666666664</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>66.199999999999989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -6787,8 +7687,14 @@
         <f t="shared" si="0"/>
         <v>53.872583333333338</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>47.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -6823,8 +7729,14 @@
         <f t="shared" si="0"/>
         <v>46.280966666666664</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1">
+        <v>15</v>
+      </c>
+      <c r="M5" s="1">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>155</v>
       </c>
@@ -6859,8 +7771,14 @@
         <f t="shared" si="0"/>
         <v>50.291466666666658</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>36</v>
+      </c>
+      <c r="M6" s="1">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>156</v>
       </c>
@@ -6895,8 +7813,14 @@
         <f t="shared" si="0"/>
         <v>30.002133333333333</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>157</v>
       </c>
@@ -6931,8 +7855,14 @@
         <f t="shared" si="0"/>
         <v>60.406850000000006</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>19</v>
+      </c>
+      <c r="M8" s="1">
+        <v>62.649999999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -6967,8 +7897,14 @@
         <f t="shared" si="0"/>
         <v>43.703566666666667</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -7003,8 +7939,14 @@
         <f t="shared" si="0"/>
         <v>68.47733333333332</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>160</v>
       </c>
@@ -7039,8 +7981,14 @@
         <f t="shared" si="0"/>
         <v>53.052549999999997</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -7075,8 +8023,14 @@
         <f t="shared" si="0"/>
         <v>50.630233333333329</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>50.699999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -7111,8 +8065,14 @@
         <f t="shared" si="0"/>
         <v>52.602699999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1">
+        <v>49.199999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>163</v>
       </c>
@@ -7147,8 +8107,14 @@
         <f t="shared" si="0"/>
         <v>64.101849999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>64.349999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -7183,8 +8149,14 @@
         <f t="shared" si="0"/>
         <v>62.903649999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>63.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -7219,8 +8191,14 @@
         <f t="shared" si="0"/>
         <v>56.044533333333327</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1">
+        <v>19</v>
+      </c>
+      <c r="M16" s="1">
+        <v>55.099999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -7255,8 +8233,14 @@
         <f t="shared" si="0"/>
         <v>48.1173</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>46.199999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>167</v>
       </c>
@@ -7291,8 +8275,14 @@
         <f t="shared" si="0"/>
         <v>38.19166666666667</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -7327,8 +8317,14 @@
         <f t="shared" si="0"/>
         <v>66.008099999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -7363,8 +8359,14 @@
         <f t="shared" si="0"/>
         <v>57.995233333333331</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>57.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -7399,8 +8401,14 @@
         <f t="shared" si="0"/>
         <v>62.324816666666663</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>62.449999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>171</v>
       </c>
@@ -7435,8 +8443,14 @@
         <f t="shared" si="0"/>
         <v>54.010216666666665</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1">
+        <v>11</v>
+      </c>
+      <c r="M22" s="1">
+        <v>53.349999999999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -7471,8 +8485,14 @@
         <f t="shared" si="0"/>
         <v>56.543500000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1">
+        <v>29</v>
+      </c>
+      <c r="M23" s="1">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>173</v>
       </c>
@@ -7507,8 +8527,14 @@
         <f t="shared" si="0"/>
         <v>58.930583333333331</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1">
+        <v>26</v>
+      </c>
+      <c r="M24" s="1">
+        <v>60.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>174</v>
       </c>
@@ -7543,8 +8569,14 @@
         <f t="shared" si="0"/>
         <v>57.394483333333326</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1">
+        <v>21</v>
+      </c>
+      <c r="M25" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>175</v>
       </c>
@@ -7579,8 +8611,14 @@
         <f t="shared" si="0"/>
         <v>67.491299999999995</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1">
+        <v>23</v>
+      </c>
+      <c r="M26" s="1">
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>176</v>
       </c>
@@ -7615,8 +8653,14 @@
         <f t="shared" si="0"/>
         <v>60.25031666666667</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1">
+        <v>11</v>
+      </c>
+      <c r="M27" s="1">
+        <v>56.55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>177</v>
       </c>
@@ -7651,8 +8695,14 @@
         <f t="shared" si="0"/>
         <v>46.34726666666667</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
+        <v>48.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>178</v>
       </c>
@@ -7687,8 +8737,14 @@
         <f t="shared" si="0"/>
         <v>58.19404999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="1">
+        <v>30</v>
+      </c>
+      <c r="M29" s="1">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>179</v>
       </c>
@@ -7723,8 +8779,14 @@
         <f t="shared" si="0"/>
         <v>64.661466666666655</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>65.199999999999989</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>180</v>
       </c>
@@ -7759,8 +8821,14 @@
         <f t="shared" si="0"/>
         <v>52.051666666666662</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="1">
+        <v>17</v>
+      </c>
+      <c r="M31" s="1">
+        <v>55.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>181</v>
       </c>
@@ -7795,8 +8863,14 @@
         <f t="shared" si="0"/>
         <v>59.995366666666662</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>60.199999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>182</v>
       </c>
@@ -7831,8 +8905,14 @@
         <f t="shared" si="0"/>
         <v>51.900233333333333</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="1">
+        <v>29</v>
+      </c>
+      <c r="M33" s="1">
+        <v>55.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -7867,8 +8947,14 @@
         <f t="shared" si="0"/>
         <v>64.709733333333332</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>184</v>
       </c>
@@ -7903,8 +8989,14 @@
         <f t="shared" si="0"/>
         <v>49.809149999999988</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -7939,8 +9031,14 @@
         <f t="shared" si="0"/>
         <v>54.130733333333332</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="1">
+        <v>4</v>
+      </c>
+      <c r="M36" s="1">
+        <v>51.949999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>186</v>
       </c>
@@ -7975,8 +9073,14 @@
         <f t="shared" si="0"/>
         <v>28.58583333333333</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -8011,8 +9115,14 @@
         <f t="shared" si="0"/>
         <v>65.248249999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>188</v>
       </c>
@@ -8047,8 +9157,14 @@
         <f t="shared" si="0"/>
         <v>55.738566666666664</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1">
+        <v>8</v>
+      </c>
+      <c r="M39" s="1">
+        <v>55.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>189</v>
       </c>
@@ -8083,8 +9199,14 @@
         <f t="shared" si="0"/>
         <v>47.9315</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>45.099999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -8119,8 +9241,14 @@
         <f t="shared" si="0"/>
         <v>69.084983333333327</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -8155,8 +9283,14 @@
         <f t="shared" si="0"/>
         <v>45.500733333333329</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="1">
+        <v>36</v>
+      </c>
+      <c r="M42" s="1">
+        <v>56.199999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>192</v>
       </c>
@@ -8191,8 +9325,14 @@
         <f t="shared" si="0"/>
         <v>56.800550000000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="1">
+        <v>17</v>
+      </c>
+      <c r="M43" s="1">
+        <v>59.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>193</v>
       </c>
@@ -8227,8 +9367,14 @@
         <f t="shared" si="0"/>
         <v>28.956233333333326</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>27.499999999999996</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -8263,8 +9409,14 @@
         <f t="shared" si="0"/>
         <v>56.238099999999996</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="1">
+        <v>34</v>
+      </c>
+      <c r="M45" s="1">
+        <v>62.899999999999991</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -8299,8 +9451,14 @@
         <f t="shared" si="0"/>
         <v>67.871733333333339</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>68.399999999999991</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -8335,8 +9493,14 @@
         <f t="shared" si="0"/>
         <v>52.232499999999995</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -8371,8 +9535,14 @@
         <f t="shared" si="0"/>
         <v>51.130166666666653</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="1">
+        <v>7</v>
+      </c>
+      <c r="M48" s="1">
+        <v>49.399999999999991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -8407,8 +9577,14 @@
         <f t="shared" si="0"/>
         <v>45.789899999999989</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="1">
+        <v>4</v>
+      </c>
+      <c r="M49" s="1">
+        <v>43.65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>199</v>
       </c>
@@ -8443,8 +9619,14 @@
         <f t="shared" si="0"/>
         <v>50.569066666666657</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>200</v>
       </c>
@@ -8479,8 +9661,14 @@
         <f t="shared" si="0"/>
         <v>74.679266666666649</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" s="1">
+        <v>20</v>
+      </c>
+      <c r="M51" s="1">
+        <v>75.25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -8498,13 +9686,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A4A384-9885-48EF-9409-BDD8E2A0903E}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8538,8 +9726,14 @@
       <c r="K1" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>201</v>
       </c>
@@ -8574,8 +9768,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>76.579070073994998</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1">
+        <v>71.099999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -8610,8 +9810,14 @@
         <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>63.404541254933328</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>203</v>
       </c>
@@ -8646,8 +9852,14 @@
         <f t="shared" si="0"/>
         <v>61.52176262326666</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>61.749999999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>204</v>
       </c>
@@ -8682,8 +9894,14 @@
         <f t="shared" si="0"/>
         <v>66.793837080889176</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>67.150000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>205</v>
       </c>
@@ -8718,8 +9936,14 @@
         <f t="shared" si="0"/>
         <v>9.3271999999999995</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>9.3999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>206</v>
       </c>
@@ -8754,8 +9978,14 @@
         <f t="shared" si="0"/>
         <v>58.888716345459997</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>8</v>
+      </c>
+      <c r="M7" s="1">
+        <v>58.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -8790,8 +10020,14 @@
         <f t="shared" si="0"/>
         <v>60.980756202403327</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>61.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>208</v>
       </c>
@@ -8826,8 +10062,14 @@
         <f t="shared" si="0"/>
         <v>55.198283885298324</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>51.149999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -8862,8 +10104,14 @@
         <f t="shared" si="0"/>
         <v>62.26417829261333</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>62.599999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>210</v>
       </c>
@@ -8898,8 +10146,14 @@
         <f t="shared" si="0"/>
         <v>66.657683094203335</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>67.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>211</v>
       </c>
@@ -8934,8 +10188,14 @@
         <f t="shared" si="0"/>
         <v>60.876748926398328</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>212</v>
       </c>
@@ -8970,8 +10230,14 @@
         <f t="shared" si="0"/>
         <v>60.462232564366666</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>60.599999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>213</v>
       </c>
@@ -9006,8 +10272,14 @@
         <f t="shared" si="0"/>
         <v>2.4849999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2.4499999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>214</v>
       </c>
@@ -9042,8 +10314,14 @@
         <f t="shared" si="0"/>
         <v>59.955459864959998</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>60.449999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>215</v>
       </c>
@@ -9078,8 +10356,14 @@
         <f t="shared" si="0"/>
         <v>33.992139220133325</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>216</v>
       </c>
@@ -9114,8 +10398,14 @@
         <f t="shared" si="0"/>
         <v>44.675791205949999</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>4</v>
+      </c>
+      <c r="M17" s="1">
+        <v>46.099999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>217</v>
       </c>
@@ -9150,8 +10440,14 @@
         <f t="shared" si="0"/>
         <v>69.06566391556666</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>69.349999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>218</v>
       </c>
@@ -9186,8 +10482,14 @@
         <f t="shared" si="0"/>
         <v>74.169565471903326</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>74.349999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>219</v>
       </c>
@@ -9222,8 +10524,14 @@
         <f t="shared" si="0"/>
         <v>14.942916666666665</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>14.799999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>220</v>
       </c>
@@ -9258,8 +10566,14 @@
         <f t="shared" si="0"/>
         <v>67.034976895301668</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>67.650000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>221</v>
       </c>
@@ -9294,8 +10608,14 @@
         <f t="shared" si="0"/>
         <v>73.195284515991673</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>73.649999999999991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>222</v>
       </c>
@@ -9330,8 +10650,14 @@
         <f t="shared" si="0"/>
         <v>64.513571778680003</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>64.599999999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -9366,8 +10692,14 @@
         <f t="shared" si="0"/>
         <v>53.75608715705166</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1">
+        <v>2</v>
+      </c>
+      <c r="M24" s="1">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>224</v>
       </c>
@@ -9402,8 +10734,14 @@
         <f t="shared" si="0"/>
         <v>70.141581969678327</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>70.349999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>225</v>
       </c>
@@ -9438,8 +10776,14 @@
         <f t="shared" si="0"/>
         <v>58.083308225068336</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1">
+        <v>28</v>
+      </c>
+      <c r="M26" s="1">
+        <v>62.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>226</v>
       </c>
@@ -9474,8 +10818,14 @@
         <f t="shared" si="0"/>
         <v>66.747009125708331</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>67.199999999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>227</v>
       </c>
@@ -9510,8 +10860,14 @@
         <f t="shared" si="0"/>
         <v>71.259889265369992</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>42.699999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>228</v>
       </c>
@@ -9546,8 +10902,14 @@
         <f t="shared" si="0"/>
         <v>50.197038947773336</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>46.099999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>229</v>
       </c>
@@ -9582,8 +10944,14 @@
         <f t="shared" si="0"/>
         <v>73.072197889269987</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="1">
+        <v>18</v>
+      </c>
+      <c r="M30" s="1">
+        <v>70.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>230</v>
       </c>
@@ -9618,8 +10986,14 @@
         <f t="shared" si="0"/>
         <v>60.097547415688325</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>60.699999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>231</v>
       </c>
@@ -9654,8 +11028,14 @@
         <f t="shared" si="0"/>
         <v>83.48595029668833</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>232</v>
       </c>
@@ -9690,8 +11070,14 @@
         <f t="shared" si="0"/>
         <v>70.633730350995833</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="1">
+        <v>17</v>
+      </c>
+      <c r="M33" s="1">
+        <v>68.150000000000006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>233</v>
       </c>
@@ -9726,8 +11112,14 @@
         <f t="shared" si="0"/>
         <v>76.30224899289999</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>76.650000000000006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>234</v>
       </c>
@@ -9762,8 +11154,14 @@
         <f t="shared" si="0"/>
         <v>56.827339674368325</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="1">
+        <v>8</v>
+      </c>
+      <c r="M35" s="1">
+        <v>55.199999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -9798,8 +11196,14 @@
         <f t="shared" si="0"/>
         <v>60.888489267786667</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>61.199999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>236</v>
       </c>
@@ -9834,8 +11238,14 @@
         <f t="shared" si="0"/>
         <v>64.088011996878336</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>64.399999999999991</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>237</v>
       </c>
@@ -9870,8 +11280,14 @@
         <f t="shared" si="0"/>
         <v>74.530655321306668</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>238</v>
       </c>
@@ -9906,8 +11322,14 @@
         <f t="shared" si="0"/>
         <v>58.706249999999997</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1">
+        <v>36</v>
+      </c>
+      <c r="M39" s="1">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -9942,8 +11364,14 @@
         <f t="shared" si="0"/>
         <v>54.62211277243</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="1">
+        <v>3</v>
+      </c>
+      <c r="M40" s="1">
+        <v>52.849999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -9978,8 +11406,14 @@
         <f t="shared" si="0"/>
         <v>54.290859018428328</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="1">
+        <v>10</v>
+      </c>
+      <c r="M41" s="1">
+        <v>54.849999999999994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>241</v>
       </c>
@@ -10014,8 +11448,14 @@
         <f t="shared" si="0"/>
         <v>68.774214628549998</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>69.099999999999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>242</v>
       </c>
@@ -10050,8 +11490,14 @@
         <f t="shared" si="0"/>
         <v>53.513940814110001</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>46.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>243</v>
       </c>
@@ -10086,8 +11532,14 @@
         <f t="shared" si="0"/>
         <v>57.741432120989998</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="1">
+        <v>13</v>
+      </c>
+      <c r="M44" s="1">
+        <v>57.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>244</v>
       </c>
@@ -10122,8 +11574,14 @@
         <f t="shared" si="0"/>
         <v>52.316441059088334</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="1">
+        <v>23</v>
+      </c>
+      <c r="M45" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>245</v>
       </c>
@@ -10158,8 +11616,14 @@
         <f t="shared" si="0"/>
         <v>70.348171025406657</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>70.849999999999994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>246</v>
       </c>
@@ -10194,8 +11658,14 @@
         <f t="shared" si="0"/>
         <v>53.123703068056663</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>46.849999999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -10230,8 +11700,14 @@
         <f t="shared" si="0"/>
         <v>62.109005669878329</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>62.449999999999996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>248</v>
       </c>
@@ -10266,8 +11742,14 @@
         <f t="shared" si="0"/>
         <v>14.701216419733329</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>14.599999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -10277,7 +11759,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -10287,7 +11769,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -10305,13 +11787,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4309DD8B-C3AE-490A-BFD6-B77DAC7DA4EB}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10345,8 +11827,14 @@
       <c r="K1" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>249</v>
       </c>
@@ -10381,8 +11869,14 @@
         <f>(0.3*J2)+((E2+I2)*0.35)</f>
         <v>69.471296454184994</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>69.849999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>250</v>
       </c>
@@ -10417,8 +11911,14 @@
         <f t="shared" ref="K3:K49" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>44.614382153079994</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>41.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>251</v>
       </c>
@@ -10453,8 +11953,14 @@
         <f t="shared" si="0"/>
         <v>63.298644614179992</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>63.55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>252</v>
       </c>
@@ -10489,8 +11995,14 @@
         <f t="shared" si="0"/>
         <v>63.455141060433327</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>63.999999999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>253</v>
       </c>
@@ -10525,8 +12037,14 @@
         <f t="shared" si="0"/>
         <v>66.846465981768333</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>67.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>254</v>
       </c>
@@ -10561,8 +12079,14 @@
         <f t="shared" si="0"/>
         <v>61.747031504999995</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>61.849999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>255</v>
       </c>
@@ -10597,8 +12121,14 @@
         <f t="shared" si="0"/>
         <v>73.407575338726659</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>256</v>
       </c>
@@ -10633,8 +12163,14 @@
         <f t="shared" si="0"/>
         <v>72.489166666666662</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -10669,8 +12205,14 @@
         <f t="shared" si="0"/>
         <v>53.131503680999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1">
+        <v>6</v>
+      </c>
+      <c r="M10" s="1">
+        <v>53.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -10705,8 +12247,14 @@
         <f t="shared" si="0"/>
         <v>84.431739069226666</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>84.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -10741,8 +12289,14 @@
         <f t="shared" si="0"/>
         <v>56.893700434426663</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1">
+        <v>2</v>
+      </c>
+      <c r="M12" s="1">
+        <v>51.55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>260</v>
       </c>
@@ -10777,8 +12331,14 @@
         <f t="shared" si="0"/>
         <v>76.665935129108334</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>76.949999999999989</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>261</v>
       </c>
@@ -10813,8 +12373,14 @@
         <f t="shared" si="0"/>
         <v>75.915630239439992</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>76.399999999999991</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -10849,8 +12415,14 @@
         <f t="shared" si="0"/>
         <v>60.039999999999992</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -10885,8 +12457,14 @@
         <f t="shared" si="0"/>
         <v>50.26422162980667</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>45.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>264</v>
       </c>
@@ -10921,8 +12499,14 @@
         <f t="shared" si="0"/>
         <v>61.42795485705733</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>60.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -10957,8 +12541,14 @@
         <f t="shared" si="0"/>
         <v>52.59426095968</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>48.349999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -10993,8 +12583,14 @@
         <f t="shared" si="0"/>
         <v>46.527383333333333</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -11029,8 +12625,14 @@
         <f t="shared" si="0"/>
         <v>77.399478588846648</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -11065,8 +12667,14 @@
         <f t="shared" si="0"/>
         <v>74.083333333333329</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>74.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>269</v>
       </c>
@@ -11101,8 +12709,14 @@
         <f t="shared" si="0"/>
         <v>62.898559555489996</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>62.949999999999989</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -11137,8 +12751,14 @@
         <f t="shared" si="0"/>
         <v>68.382735392698336</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>271</v>
       </c>
@@ -11173,8 +12793,14 @@
         <f t="shared" si="0"/>
         <v>63.771232847416655</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -11209,8 +12835,14 @@
         <f t="shared" si="0"/>
         <v>57.987718325576665</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1">
+        <v>19</v>
+      </c>
+      <c r="M25" s="1">
+        <v>58.099999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -11245,8 +12877,14 @@
         <f t="shared" si="0"/>
         <v>69.021035989673322</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>69.150000000000006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -11281,8 +12919,14 @@
         <f t="shared" si="0"/>
         <v>69.1273022524</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -11317,8 +12961,14 @@
         <f t="shared" si="0"/>
         <v>67.46846563799933</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -11353,8 +13003,14 @@
         <f t="shared" si="0"/>
         <v>62.031331927883329</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>62.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -11389,8 +13045,14 @@
         <f t="shared" si="0"/>
         <v>64.961596857549992</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>65.399999999999991</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -11425,8 +13087,14 @@
         <f t="shared" si="0"/>
         <v>39.211666666666666</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>39.199999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -11461,8 +13129,14 @@
         <f t="shared" si="0"/>
         <v>66.665020470656657</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>67.099999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>280</v>
       </c>
@@ -11497,8 +13171,14 @@
         <f t="shared" si="0"/>
         <v>39.18532478978333</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>39.450000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>281</v>
       </c>
@@ -11533,8 +13213,14 @@
         <f t="shared" si="0"/>
         <v>58.024634274013323</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="1">
+        <v>11</v>
+      </c>
+      <c r="M34" s="1">
+        <v>60.599999999999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -11569,8 +13255,14 @@
         <f t="shared" si="0"/>
         <v>64.787983109516659</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>65.199999999999989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -11605,8 +13297,14 @@
         <f t="shared" si="0"/>
         <v>63.310324086268338</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>284</v>
       </c>
@@ -11641,8 +13339,14 @@
         <f t="shared" si="0"/>
         <v>32.347499999999997</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>285</v>
       </c>
@@ -11677,8 +13381,14 @@
         <f t="shared" si="0"/>
         <v>70.296250000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>70.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>286</v>
       </c>
@@ -11713,8 +13423,14 @@
         <f t="shared" si="0"/>
         <v>54.822018460479995</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1">
+        <v>10</v>
+      </c>
+      <c r="M39" s="1">
+        <v>53.65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -11749,8 +13465,14 @@
         <f t="shared" si="0"/>
         <v>65.835949999999997</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="1">
+        <v>2</v>
+      </c>
+      <c r="M40" s="1">
+        <v>63.099999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>288</v>
       </c>
@@ -11785,8 +13507,14 @@
         <f t="shared" si="0"/>
         <v>51.036022746279997</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>47.699999999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>289</v>
       </c>
@@ -11821,8 +13549,14 @@
         <f t="shared" si="0"/>
         <v>55.60833011199999</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="1">
+        <v>18</v>
+      </c>
+      <c r="M42" s="1">
+        <v>56.649999999999991</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>290</v>
       </c>
@@ -11857,8 +13591,14 @@
         <f t="shared" si="0"/>
         <v>69.943669462813332</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>70.149999999999991</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -11893,8 +13633,14 @@
         <f t="shared" si="0"/>
         <v>51.926743758501658</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>45.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>292</v>
       </c>
@@ -11929,8 +13675,14 @@
         <f t="shared" si="0"/>
         <v>74.315787171233339</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -11965,8 +13717,14 @@
         <f t="shared" si="0"/>
         <v>83.584363750816664</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="1">
+        <v>30</v>
+      </c>
+      <c r="M46" s="1">
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -12001,8 +13759,14 @@
         <f t="shared" si="0"/>
         <v>28.742387461924999</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>27.449999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>295</v>
       </c>
@@ -12037,8 +13801,14 @@
         <f t="shared" si="0"/>
         <v>37.732315025376664</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -12073,8 +13843,14 @@
         <f t="shared" si="0"/>
         <v>58.365339994759992</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="1">
+        <v>8</v>
+      </c>
+      <c r="M49" s="1">
+        <v>58.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -12084,7 +13860,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -12094,7 +13870,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>

--- a/CoursesList/Grades_PAO_II_2025_FEM.xlsx
+++ b/CoursesList/Grades_PAO_II_2025_FEM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisp\Desktop\Papers\J4 Tutor Socratico\Notas PAO II 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF018A8-B20C-4108-80F4-4274E32688EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339836EB-9999-4BEC-9E1B-6E9DD3B43F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="302">
   <si>
     <t>codigo</t>
   </si>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>FINAL CON 3er Examen</t>
+  </si>
+  <si>
+    <t>Situacion</t>
   </si>
 </sst>
 </file>
@@ -982,17 +985,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1314,13 +1331,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6683928A-C7F0-4796-BECC-A9961919393E}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1360,8 +1377,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1400,10 +1420,15 @@
         <v>75</v>
       </c>
       <c r="M2" s="1">
-        <v>62.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>62.884863484183327</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1442,10 +1467,15 @@
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>14.95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M3:M52" si="1">(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>14.797516666666667</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N53" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1484,10 +1514,15 @@
         <v>42</v>
       </c>
       <c r="M4" s="1">
-        <v>50.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.119294857787992</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1526,10 +1561,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>19.785604644589998</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1568,10 +1608,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>39.349999999999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>39.32350722348</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1610,10 +1655,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>64.699999999999989</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.138190388916541</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1652,10 +1702,15 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.941783105006664</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1694,10 +1749,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>72.230389233971465</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1736,10 +1796,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>62.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.501165661442329</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1778,10 +1843,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.959740636045908</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1820,10 +1890,15 @@
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.532166666666669</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1862,10 +1937,15 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>35.450000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>35.487683333333337</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1904,10 +1984,15 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>65.349999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.221322219439998</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1946,10 +2031,15 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>39.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>43.046863010188765</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1988,10 +2078,15 @@
         <v>47</v>
       </c>
       <c r="M16" s="1">
-        <v>56.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57.38199159880233</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2030,10 +2125,15 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>60.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.415252103591655</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2072,10 +2172,15 @@
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>66.150000000000006</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.848271180127341</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2114,10 +2219,15 @@
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>25.049999999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>26.537529838186</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2156,10 +2266,15 @@
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>70.199999999999989</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.906686860181452</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2198,10 +2313,15 @@
         <v>87</v>
       </c>
       <c r="M21" s="1">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>82.884866054490658</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2240,10 +2360,15 @@
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.84628676664633</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2282,10 +2407,15 @@
         <v>60</v>
       </c>
       <c r="M23" s="1">
-        <v>58.249999999999993</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>58.127499999999998</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2324,10 +2454,15 @@
         <v>42</v>
       </c>
       <c r="M24" s="1">
-        <v>44.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>45.222698507212066</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2366,10 +2501,15 @@
         <v>41</v>
       </c>
       <c r="M25" s="1">
-        <v>53.349999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.209391106687988</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2408,10 +2548,15 @@
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>65.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.409636174359989</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2450,10 +2595,15 @@
         <v>66</v>
       </c>
       <c r="M27" s="1">
-        <v>55.55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.467918696499993</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2492,10 +2642,15 @@
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>60.349999999999994</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.02006994558333</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2534,10 +2689,15 @@
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>71.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>71.116935802394664</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2576,10 +2736,15 @@
         <v>31</v>
       </c>
       <c r="M30" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>47.697375398289495</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2618,10 +2783,15 @@
         <v>51</v>
       </c>
       <c r="M31" s="1">
-        <v>52.399999999999991</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>52.483468896916989</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2660,10 +2830,15 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.422410644476344</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2702,10 +2877,15 @@
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <v>36.349999999999994</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>38.437368190098326</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2744,10 +2924,15 @@
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>68.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.040917472272895</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2786,10 +2971,15 @@
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>71.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>71.437484006197323</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2828,10 +3018,15 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>65.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.850395195202665</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2870,10 +3065,15 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>70.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.280073091931655</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2912,10 +3112,15 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>76.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>76.528557330033991</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2954,10 +3159,15 @@
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>60.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.916247112562985</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2996,10 +3206,15 @@
         <v>61</v>
       </c>
       <c r="M40" s="1">
-        <v>56.349999999999994</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.45253381371333</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -3038,10 +3253,15 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.541206149475002</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -3080,10 +3300,15 @@
         <v>0</v>
       </c>
       <c r="M42" s="1">
-        <v>68.949999999999989</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.642904844672202</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -3122,10 +3347,15 @@
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>68.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.031245652004657</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -3164,10 +3394,15 @@
         <v>0</v>
       </c>
       <c r="M44" s="1">
-        <v>81.149999999999991</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>80.537912816238318</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -3206,10 +3441,15 @@
         <v>43</v>
       </c>
       <c r="M45" s="1">
-        <v>52.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.854286671819629</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -3248,10 +3488,15 @@
         <v>64.27000000000001</v>
       </c>
       <c r="M46" s="1">
-        <v>60.144500000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.941499999999998</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -3290,10 +3535,15 @@
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>68.599999999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.470817339530669</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -3332,10 +3582,15 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>64.649999999999991</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.49882708576034</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -3374,10 +3629,15 @@
         <v>67</v>
       </c>
       <c r="M49" s="1">
-        <v>73.449999999999989</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>73.403333333333336</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -3416,10 +3676,15 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.696345225236328</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -3458,10 +3723,15 @@
         <v>41</v>
       </c>
       <c r="M51" s="1">
-        <v>56.199999999999996</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.204083333333323</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -3500,7 +3770,18 @@
         <v>54</v>
       </c>
       <c r="M52" s="1">
-        <v>67.25</v>
+        <f t="shared" si="1"/>
+        <v>71.608144963755336</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N53">
+        <f>COUNTIF(N2:N52,"AP")</f>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3511,13 +3792,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06D9429-8703-4320-B402-8BE6A17251E5}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3557,8 +3838,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -3596,11 +3880,16 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>40.65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M2" s="1">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>44.880566666666667</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -3638,11 +3927,16 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>61.749999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M3" s="1">
+        <f>(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>61.242033333333325</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N43" si="1">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3680,11 +3974,16 @@
       <c r="L4" s="1">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>20.549999999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M4" s="1">
+        <f>(0.7*(SUM(E4,I4,L4)-MIN(E4,I4,L4))/2)+(0.3*J4)</f>
+        <v>20.52923333333333</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -3722,11 +4021,16 @@
       <c r="L5" s="1">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>43.349999999999994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M5" s="1">
+        <f>(0.7*(SUM(E5,I5,L5)-MIN(E5,I5,L5))/2)+(0.3*J5)</f>
+        <v>49.736566666666661</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -3764,11 +4068,16 @@
       <c r="L6" s="1">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>31.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M6" s="1">
+        <f>(0.7*(SUM(E6,I6,L6)-MIN(E6,I6,L6))/2)+(0.3*J6)</f>
+        <v>19.464799999999997</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -3804,13 +4113,18 @@
         <v>51.197399999999995</v>
       </c>
       <c r="L7" s="1">
-        <v>18</v>
-      </c>
-      <c r="M7">
-        <v>51.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="M7" s="1">
+        <f>(0.7*(SUM(E7,I7,L7)-MIN(E7,I7,L7))/2)+(0.3*J7)</f>
+        <v>51.98</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -3848,11 +4162,16 @@
       <c r="L8" s="1">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>37.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M8" s="1">
+        <f>(0.7*(SUM(E8,I8,L8)-MIN(E8,I8,L8))/2)+(0.3*J8)</f>
+        <v>37.052933333333328</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3890,11 +4209,16 @@
       <c r="L9" s="1">
         <v>0</v>
       </c>
-      <c r="M9">
-        <v>64.849999999999994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M9" s="1">
+        <f>(0.7*(SUM(E9,I9,L9)-MIN(E9,I9,L9))/2)+(0.3*J9)</f>
+        <v>64.725166666666667</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3932,11 +4256,16 @@
       <c r="L10" s="1">
         <v>0</v>
       </c>
-      <c r="M10">
-        <v>62.949999999999989</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="1">
+        <f>(0.7*(SUM(E10,I10,L10)-MIN(E10,I10,L10))/2)+(0.3*J10)</f>
+        <v>62.599999999999994</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -3974,11 +4303,16 @@
       <c r="L11" s="1">
         <v>0</v>
       </c>
-      <c r="M11">
-        <v>16.849999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M11" s="1">
+        <f>(0.7*(SUM(E11,I11,L11)-MIN(E11,I11,L11))/2)+(0.3*J11)</f>
+        <v>16.870066666666666</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -4016,11 +4350,16 @@
       <c r="L12" s="1">
         <v>0</v>
       </c>
-      <c r="M12">
-        <v>39.199999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M12" s="1">
+        <f>(0.7*(SUM(E12,I12,L12)-MIN(E12,I12,L12))/2)+(0.3*J12)</f>
+        <v>46.525733333333328</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -4058,11 +4397,16 @@
       <c r="L13" s="1">
         <v>0</v>
       </c>
-      <c r="M13">
-        <v>61.65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M13" s="1">
+        <f>(0.7*(SUM(E13,I13,L13)-MIN(E13,I13,L13))/2)+(0.3*J13)</f>
+        <v>61.27806666666666</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -4100,11 +4444,16 @@
       <c r="L14" s="1">
         <v>0</v>
       </c>
-      <c r="M14">
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="1">
+        <f>(0.7*(SUM(E14,I14,L14)-MIN(E14,I14,L14))/2)+(0.3*J14)</f>
+        <v>29.993099999999998</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -4142,11 +4491,16 @@
       <c r="L15" s="1">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M15" s="1">
+        <f>(0.7*(SUM(E15,I15,L15)-MIN(E15,I15,L15))/2)+(0.3*J15)</f>
+        <v>26.971666666666664</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -4184,11 +4538,16 @@
       <c r="L16" s="1">
         <v>0</v>
       </c>
-      <c r="M16">
-        <v>66.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M16" s="1">
+        <f>(0.7*(SUM(E16,I16,L16)-MIN(E16,I16,L16))/2)+(0.3*J16)</f>
+        <v>65.513333333333335</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -4226,11 +4585,16 @@
       <c r="L17" s="1">
         <v>0</v>
       </c>
-      <c r="M17">
-        <v>35.449999999999996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="1">
+        <f>(0.7*(SUM(E17,I17,L17)-MIN(E17,I17,L17))/2)+(0.3*J17)</f>
+        <v>35.58626666666666</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -4266,13 +4630,18 @@
         <v>48.214866666666666</v>
       </c>
       <c r="L18" s="1">
-        <v>13</v>
-      </c>
-      <c r="M18">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="M18" s="1">
+        <f>(0.7*(SUM(E18,I18,L18)-MIN(E18,I18,L18))/2)+(0.3*J18)</f>
+        <v>48.38986666666667</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -4308,13 +4677,18 @@
         <v>46.357933333333328</v>
       </c>
       <c r="L19" s="1">
-        <v>13</v>
-      </c>
-      <c r="M19">
-        <v>45.65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="M19" s="1">
+        <f>(0.7*(SUM(E19,I19,L19)-MIN(E19,I19,L19))/2)+(0.3*J19)</f>
+        <v>46.357933333333328</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -4350,13 +4724,18 @@
         <v>69.188866666666655</v>
       </c>
       <c r="L20" s="1">
-        <v>12</v>
-      </c>
-      <c r="M20">
-        <v>65.399999999999991</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="M20" s="1">
+        <f>(0.7*(SUM(E20,I20,L20)-MIN(E20,I20,L20))/2)+(0.3*J20)</f>
+        <v>69.188866666666655</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -4394,11 +4773,16 @@
       <c r="L21" s="1">
         <v>0</v>
       </c>
-      <c r="M21">
-        <v>43.699999999999996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="1">
+        <f>(0.7*(SUM(E21,I21,L21)-MIN(E21,I21,L21))/2)+(0.3*J21)</f>
+        <v>50.450916666666657</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -4434,13 +4818,18 @@
         <v>51.700150000000001</v>
       </c>
       <c r="L22" s="1">
-        <v>10</v>
-      </c>
-      <c r="M22">
-        <v>50.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="M22" s="1">
+        <f>(0.7*(SUM(E22,I22,L22)-MIN(E22,I22,L22))/2)+(0.3*J22)</f>
+        <v>51.700150000000001</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -4478,11 +4867,16 @@
       <c r="L23" s="1">
         <v>0</v>
       </c>
-      <c r="M23">
-        <v>41.999999999999993</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="1">
+        <f>(0.7*(SUM(E23,I23,L23)-MIN(E23,I23,L23))/2)+(0.3*J23)</f>
+        <v>48.577666666666659</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4520,11 +4914,16 @@
       <c r="L24" s="1">
         <v>0</v>
       </c>
-      <c r="M24">
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M24" s="1">
+        <f>(0.7*(SUM(E24,I24,L24)-MIN(E24,I24,L24))/2)+(0.3*J24)</f>
+        <v>46.633266666666664</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>84</v>
       </c>
@@ -4562,11 +4961,16 @@
       <c r="L25" s="1">
         <v>0</v>
       </c>
-      <c r="M25">
-        <v>42.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M25" s="1">
+        <f>(0.7*(SUM(E25,I25,L25)-MIN(E25,I25,L25))/2)+(0.3*J25)</f>
+        <v>47.198116666666664</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -4604,11 +5008,16 @@
       <c r="L26" s="1">
         <v>0</v>
       </c>
-      <c r="M26">
-        <v>23.849999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M26" s="1">
+        <f>(0.7*(SUM(E26,I26,L26)-MIN(E26,I26,L26))/2)+(0.3*J26)</f>
+        <v>23.894333333333329</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -4646,11 +5055,16 @@
       <c r="L27" s="1">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M27" s="1">
+        <f>(0.7*(SUM(E27,I27,L27)-MIN(E27,I27,L27))/2)+(0.3*J27)</f>
+        <v>13.581466666666664</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -4688,11 +5102,16 @@
       <c r="L28" s="1">
         <v>0</v>
       </c>
-      <c r="M28">
-        <v>25.999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M28" s="1">
+        <f>(0.7*(SUM(E28,I28,L28)-MIN(E28,I28,L28))/2)+(0.3*J28)</f>
+        <v>25.754766666666665</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>88</v>
       </c>
@@ -4730,11 +5149,16 @@
       <c r="L29" s="1">
         <v>0</v>
       </c>
-      <c r="M29">
-        <v>60.099999999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M29" s="1">
+        <f>(0.7*(SUM(E29,I29,L29)-MIN(E29,I29,L29))/2)+(0.3*J29)</f>
+        <v>59.532066666666658</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -4772,11 +5196,16 @@
       <c r="L30" s="1">
         <v>0</v>
       </c>
-      <c r="M30">
-        <v>60.099999999999994</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M30" s="1">
+        <f>(0.7*(SUM(E30,I30,L30)-MIN(E30,I30,L30))/2)+(0.3*J30)</f>
+        <v>59.80436666666666</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -4814,11 +5243,16 @@
       <c r="L31" s="1">
         <v>0</v>
       </c>
-      <c r="M31">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M31" s="1">
+        <f>(0.7*(SUM(E31,I31,L31)-MIN(E31,I31,L31))/2)+(0.3*J31)</f>
+        <v>42.542833333333334</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -4856,11 +5290,16 @@
       <c r="L32" s="1">
         <v>0</v>
       </c>
-      <c r="M32">
-        <v>60.199999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M32" s="1">
+        <f>(0.7*(SUM(E32,I32,L32)-MIN(E32,I32,L32))/2)+(0.3*J32)</f>
+        <v>59.60126666666666</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -4896,13 +5335,18 @@
         <v>49.428333333333327</v>
       </c>
       <c r="L33" s="1">
-        <v>14</v>
-      </c>
-      <c r="M33">
-        <v>49.649999999999991</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="M33" s="1">
+        <f>(0.7*(SUM(E33,I33,L33)-MIN(E33,I33,L33))/2)+(0.3*J33)</f>
+        <v>49.510000000000005</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -4938,13 +5382,18 @@
         <v>56.29</v>
       </c>
       <c r="L34" s="1">
-        <v>37</v>
-      </c>
-      <c r="M34">
-        <v>63.499999999999993</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="M34" s="1">
+        <f>(0.7*(SUM(E34,I34,L34)-MIN(E34,I34,L34))/2)+(0.3*J34)</f>
+        <v>63.604999999999997</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -4982,11 +5431,16 @@
       <c r="L35" s="1">
         <v>0</v>
       </c>
-      <c r="M35">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M35" s="1">
+        <f>(0.7*(SUM(E35,I35,L35)-MIN(E35,I35,L35))/2)+(0.3*J35)</f>
+        <v>37.134999999999998</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -5022,13 +5476,18 @@
         <v>55.454716666666663</v>
       </c>
       <c r="L36" s="1">
-        <v>20</v>
-      </c>
-      <c r="M36">
-        <v>54.349999999999994</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="M36" s="1">
+        <f>(0.7*(SUM(E36,I36,L36)-MIN(E36,I36,L36))/2)+(0.3*J36)</f>
+        <v>55.45471666666667</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>96</v>
       </c>
@@ -5066,11 +5525,16 @@
       <c r="L37" s="1">
         <v>0</v>
       </c>
-      <c r="M37">
-        <v>39.099999999999994</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M37" s="1">
+        <f>(0.7*(SUM(E37,I37,L37)-MIN(E37,I37,L37))/2)+(0.3*J37)</f>
+        <v>43.522133333333336</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
@@ -5108,11 +5572,16 @@
       <c r="L38" s="1">
         <v>0</v>
       </c>
-      <c r="M38">
-        <v>29.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M38" s="1">
+        <f>(0.7*(SUM(E38,I38,L38)-MIN(E38,I38,L38))/2)+(0.3*J38)</f>
+        <v>31.352266666666665</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -5150,11 +5619,16 @@
       <c r="L39" s="1">
         <v>0</v>
       </c>
-      <c r="M39">
-        <v>2.0999999999999996</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M39" s="1">
+        <f>(0.7*(SUM(E39,I39,L39)-MIN(E39,I39,L39))/2)+(0.3*J39)</f>
+        <v>1.948333333333333</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -5192,11 +5666,16 @@
       <c r="L40" s="1">
         <v>0</v>
       </c>
-      <c r="M40">
-        <v>67.55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M40" s="1">
+        <f>(0.7*(SUM(E40,I40,L40)-MIN(E40,I40,L40))/2)+(0.3*J40)</f>
+        <v>67.214233333333326</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -5234,11 +5713,16 @@
       <c r="L41" s="1">
         <v>0</v>
       </c>
-      <c r="M41">
-        <v>2.4499999999999997</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M41" s="1">
+        <f>(0.7*(SUM(E41,I41,L41)-MIN(E41,I41,L41))/2)+(0.3*J41)</f>
+        <v>2.4033333333333333</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -5276,11 +5760,16 @@
       <c r="L42" s="1">
         <v>0</v>
       </c>
-      <c r="M42">
-        <v>60.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M42" s="1">
+        <f>(0.7*(SUM(E42,I42,L42)-MIN(E42,I42,L42))/2)+(0.3*J42)</f>
+        <v>60.004599999999996</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="1"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -5318,11 +5807,16 @@
       <c r="L43" s="1">
         <v>0</v>
       </c>
-      <c r="M43">
-        <v>44.149999999999991</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M43" s="1">
+        <f>(0.7*(SUM(E43,I43,L43)-MIN(E43,I43,L43))/2)+(0.3*J43)</f>
+        <v>43.982933333333328</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="1"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -5331,8 +5825,12 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N44" s="3">
+        <f>COUNTIF(N2:N43,"AP")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -5342,7 +5840,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -5352,7 +5850,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -5362,7 +5860,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -5420,13 +5918,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D643C4-EA4F-4806-B013-93EEAF775219}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5466,8 +5964,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -5505,11 +6006,16 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>9.5999999999999979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M2" s="1">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>9.5474999999999977</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -5547,11 +6053,16 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>72.150000000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M49" si="1">(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>71.64545904517999</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N49" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -5589,11 +6100,16 @@
       <c r="L4" s="1">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>9.2499999999999982</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M4" s="1">
+        <f t="shared" si="1"/>
+        <v>9.2671499999999991</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
@@ -5629,13 +6145,18 @@
         <v>43.145317058333326</v>
       </c>
       <c r="L5" s="1">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="1"/>
+        <v>43.145317058333326</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -5673,11 +6194,16 @@
       <c r="L6" s="1">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>35.199999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M6" s="1">
+        <f t="shared" si="1"/>
+        <v>38.850499936708324</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>108</v>
       </c>
@@ -5713,13 +6239,18 @@
         <v>51.877958863094996</v>
       </c>
       <c r="L7" s="1">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>57.699999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="1"/>
+        <v>57.589446666666667</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -5755,13 +6286,18 @@
         <v>51.277088810638332</v>
       </c>
       <c r="L8" s="1">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>55.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="1"/>
+        <v>55.284588810638333</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5799,11 +6335,16 @@
       <c r="L9" s="1">
         <v>0</v>
       </c>
-      <c r="M9">
-        <v>16.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M9" s="1">
+        <f t="shared" si="1"/>
+        <v>16.844609416426668</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -5841,11 +6382,16 @@
       <c r="L10" s="1">
         <v>0</v>
       </c>
-      <c r="M10">
-        <v>33.099999999999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="1">
+        <f t="shared" si="1"/>
+        <v>35.054516666666665</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -5883,11 +6429,16 @@
       <c r="L11" s="1">
         <v>0</v>
       </c>
-      <c r="M11">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M11" s="1">
+        <f t="shared" si="1"/>
+        <v>46.416407986434166</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -5925,11 +6476,16 @@
       <c r="L12" s="1">
         <v>0</v>
       </c>
-      <c r="M12">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M12" s="1">
+        <f t="shared" si="1"/>
+        <v>14.864999999999998</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
@@ -5967,11 +6523,16 @@
       <c r="L13" s="1">
         <v>0</v>
       </c>
-      <c r="M13">
-        <v>14.35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M13" s="1">
+        <f t="shared" si="1"/>
+        <v>14.303341013523333</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
@@ -6009,11 +6570,16 @@
       <c r="L14" s="1">
         <v>0</v>
       </c>
-      <c r="M14">
-        <v>35.699999999999996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="1">
+        <f t="shared" si="1"/>
+        <v>42.528398473219163</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -6051,11 +6617,16 @@
       <c r="L15" s="1">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>65.849999999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M15" s="1">
+        <f t="shared" si="1"/>
+        <v>65.358167211075823</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>117</v>
       </c>
@@ -6093,11 +6664,16 @@
       <c r="L16" s="1">
         <v>0</v>
       </c>
-      <c r="M16">
-        <v>29.449999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M16" s="1">
+        <f t="shared" si="1"/>
+        <v>31.178409330561664</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -6135,11 +6711,16 @@
       <c r="L17" s="1">
         <v>0</v>
       </c>
-      <c r="M17">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="1">
+        <f t="shared" si="1"/>
+        <v>2.9846499999999998</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -6175,13 +6756,18 @@
         <v>68.820189999999997</v>
       </c>
       <c r="L18" s="1">
-        <v>25</v>
-      </c>
-      <c r="M18">
-        <v>68.349999999999994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="M18" s="1">
+        <f t="shared" si="1"/>
+        <v>68.820189999999997</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -6217,13 +6803,18 @@
         <v>49.022162652437501</v>
       </c>
       <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19">
-        <v>48.349999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" si="1"/>
+        <v>49.022162652437501</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -6259,13 +6850,18 @@
         <v>48.652782396093336</v>
       </c>
       <c r="L20" s="1">
-        <v>13</v>
-      </c>
-      <c r="M20">
-        <v>47.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="1"/>
+        <v>48.652782396093336</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>122</v>
       </c>
@@ -6303,11 +6899,16 @@
       <c r="L21" s="1">
         <v>0</v>
       </c>
-      <c r="M21">
-        <v>41.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="1">
+        <f t="shared" si="1"/>
+        <v>47.798020578049993</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -6345,11 +6946,16 @@
       <c r="L22" s="1">
         <v>0</v>
       </c>
-      <c r="M22">
-        <v>38.449999999999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M22" s="1">
+        <f t="shared" si="1"/>
+        <v>42.086733333333328</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -6387,11 +6993,16 @@
       <c r="L23" s="1">
         <v>0</v>
       </c>
-      <c r="M23">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="1">
+        <f t="shared" si="1"/>
+        <v>3.2849999999999997</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -6429,11 +7040,16 @@
       <c r="L24" s="1">
         <v>0</v>
       </c>
-      <c r="M24">
-        <v>64.599999999999994</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M24" s="1">
+        <f t="shared" si="1"/>
+        <v>63.246590686053338</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -6471,11 +7087,16 @@
       <c r="L25" s="1">
         <v>0</v>
       </c>
-      <c r="M25">
-        <v>41.849999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M25" s="1">
+        <f t="shared" si="1"/>
+        <v>44.558657298246665</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -6513,11 +7134,16 @@
       <c r="L26" s="1">
         <v>0</v>
       </c>
-      <c r="M26">
-        <v>63.649999999999991</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M26" s="1">
+        <f t="shared" si="1"/>
+        <v>63.31672282112666</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -6555,11 +7181,16 @@
       <c r="L27" s="1">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>34.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M27" s="1">
+        <f t="shared" si="1"/>
+        <v>37.302555112495</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>129</v>
       </c>
@@ -6597,11 +7228,16 @@
       <c r="L28" s="1">
         <v>0</v>
       </c>
-      <c r="M28">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M28" s="1">
+        <f t="shared" si="1"/>
+        <v>1.7174999999999998</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -6639,11 +7275,16 @@
       <c r="L29" s="1">
         <v>0</v>
       </c>
-      <c r="M29">
-        <v>72.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M29" s="1">
+        <f t="shared" si="1"/>
+        <v>68.705936666666659</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -6681,11 +7322,16 @@
       <c r="L30" s="1">
         <v>0</v>
       </c>
-      <c r="M30">
-        <v>35.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M30" s="1">
+        <f t="shared" si="1"/>
+        <v>44.395349999999993</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -6721,13 +7367,18 @@
         <v>39.72528158918</v>
       </c>
       <c r="L31" s="1">
-        <v>5</v>
-      </c>
-      <c r="M31">
-        <v>37.549999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="M31" s="1">
+        <f t="shared" si="1"/>
+        <v>39.72528158918</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -6763,13 +7414,18 @@
         <v>57.422683333333332</v>
       </c>
       <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32">
-        <v>51.749999999999993</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="M32" s="1">
+        <f t="shared" si="1"/>
+        <v>57.422683333333332</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>134</v>
       </c>
@@ -6805,13 +7461,18 @@
         <v>62.065032493633332</v>
       </c>
       <c r="L33" s="1">
-        <v>20</v>
-      </c>
-      <c r="M33">
-        <v>61.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="M33" s="1">
+        <f t="shared" si="1"/>
+        <v>62.065032493633332</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>135</v>
       </c>
@@ -6847,13 +7508,18 @@
         <v>53.910223042505002</v>
       </c>
       <c r="L34" s="1">
-        <v>4</v>
-      </c>
-      <c r="M34">
-        <v>50.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="M34" s="1">
+        <f t="shared" si="1"/>
+        <v>53.910223042505002</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>136</v>
       </c>
@@ -6891,11 +7557,16 @@
       <c r="L35" s="1">
         <v>0</v>
       </c>
-      <c r="M35">
-        <v>75.949999999999989</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M35" s="1">
+        <f t="shared" si="1"/>
+        <v>75.564673333333332</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -6933,11 +7604,16 @@
       <c r="L36" s="1">
         <v>0</v>
       </c>
-      <c r="M36">
-        <v>60.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M36" s="1">
+        <f t="shared" si="1"/>
+        <v>60.152839999999998</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -6975,11 +7651,16 @@
       <c r="L37" s="1">
         <v>0</v>
       </c>
-      <c r="M37">
-        <v>15.249999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M37" s="1">
+        <f t="shared" si="1"/>
+        <v>16.606311456733334</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>139</v>
       </c>
@@ -7017,11 +7698,16 @@
       <c r="L38" s="1">
         <v>0</v>
       </c>
-      <c r="M38">
-        <v>43.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M38" s="1">
+        <f t="shared" si="1"/>
+        <v>49.199886352385832</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -7059,11 +7745,16 @@
       <c r="L39" s="1">
         <v>0</v>
       </c>
-      <c r="M39">
-        <v>37.599999999999994</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M39" s="1">
+        <f t="shared" si="1"/>
+        <v>41.14613587817999</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>141</v>
       </c>
@@ -7101,11 +7792,16 @@
       <c r="L40" s="1">
         <v>0</v>
       </c>
-      <c r="M40">
-        <v>26.699999999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M40" s="1">
+        <f t="shared" si="1"/>
+        <v>29.912213478325832</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -7141,13 +7837,18 @@
         <v>51.458681404008331</v>
       </c>
       <c r="L41" s="1">
-        <v>10</v>
-      </c>
-      <c r="M41">
-        <v>52.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="M41" s="1">
+        <f t="shared" si="1"/>
+        <v>51.990639999999985</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -7183,13 +7884,18 @@
         <v>33.317552604883332</v>
       </c>
       <c r="L42" s="1">
-        <v>4</v>
-      </c>
-      <c r="M42">
-        <v>32.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="M42" s="1">
+        <f t="shared" si="1"/>
+        <v>33.317552604883332</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -7225,13 +7931,18 @@
         <v>68.018712568516662</v>
       </c>
       <c r="L43" s="1">
-        <v>34</v>
-      </c>
-      <c r="M43">
-        <v>73.199999999999989</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="M43" s="1">
+        <f t="shared" si="1"/>
+        <v>72.651666666666671</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -7269,11 +7980,16 @@
       <c r="L44" s="1">
         <v>0</v>
       </c>
-      <c r="M44">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M44" s="1">
+        <f t="shared" si="1"/>
+        <v>30.335816666666666</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -7311,11 +8027,16 @@
       <c r="L45" s="1">
         <v>0</v>
       </c>
-      <c r="M45">
-        <v>35.15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M45" s="1">
+        <f t="shared" si="1"/>
+        <v>43.512636639874998</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -7351,13 +8072,18 @@
         <v>50.160296666666667</v>
       </c>
       <c r="L46" s="1">
-        <v>7</v>
-      </c>
-      <c r="M46">
-        <v>46.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="1"/>
+        <v>50.160296666666667</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -7395,11 +8121,16 @@
       <c r="L47" s="1">
         <v>0</v>
       </c>
-      <c r="M47">
-        <v>29.949999999999996</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M47" s="1">
+        <f t="shared" si="1"/>
+        <v>30.922534937441668</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -7435,13 +8166,18 @@
         <v>28.16709679736833</v>
       </c>
       <c r="L48" s="1">
-        <v>7</v>
-      </c>
-      <c r="M48">
-        <v>26.849999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="1"/>
+        <v>28.16709679736833</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -7477,13 +8213,18 @@
         <v>49.212278001343336</v>
       </c>
       <c r="L49" s="1">
-        <v>8</v>
-      </c>
-      <c r="M49">
-        <v>47.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="1"/>
+        <v>49.212278001343336</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -7492,8 +8233,12 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N50">
+        <f>COUNTIF(N2:N49,"AP")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -7503,7 +8248,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -7521,13 +8266,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50D314B-C5D2-4604-9044-09199DFEB247}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7567,8 +8312,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7604,13 +8352,18 @@
         <v>64.533683333333329</v>
       </c>
       <c r="L2" s="1">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="M2" s="1">
-        <v>67.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>67.835349999999991</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -7642,17 +8395,22 @@
         <v>48</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <f t="shared" ref="K3:M51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>66.032466666666664</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>66.199999999999989</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M3:M51" si="1">(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>66.032466666666664</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N51" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -7691,10 +8449,15 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>47.95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.872583333333338</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -7730,13 +8493,18 @@
         <v>46.280966666666664</v>
       </c>
       <c r="L5" s="1">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="M5" s="1">
-        <v>49.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>49.641666666666666</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>155</v>
       </c>
@@ -7772,13 +8540,18 @@
         <v>50.291466666666658</v>
       </c>
       <c r="L6" s="1">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="M6" s="1">
-        <v>59.999999999999993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.033133333333325</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>156</v>
       </c>
@@ -7817,10 +8590,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>28.45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>30.002133333333333</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>157</v>
       </c>
@@ -7856,13 +8634,18 @@
         <v>60.406850000000006</v>
       </c>
       <c r="L8" s="1">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="M8" s="1">
-        <v>62.649999999999991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.603333333333339</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -7901,10 +8684,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>43.703566666666667</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -7943,10 +8731,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.47733333333332</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>160</v>
       </c>
@@ -7985,10 +8778,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>49.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.052549999999997</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -8024,13 +8822,18 @@
         <v>50.630233333333329</v>
       </c>
       <c r="L12" s="1">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="M12" s="1">
-        <v>50.699999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50.664999999999999</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -8066,13 +8869,18 @@
         <v>52.602699999999999</v>
       </c>
       <c r="L13" s="1">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="M13" s="1">
-        <v>49.199999999999996</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>52.602699999999999</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>163</v>
       </c>
@@ -8111,10 +8919,15 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>64.349999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.101849999999999</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -8153,10 +8966,15 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>63.45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.903649999999999</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -8192,13 +9010,18 @@
         <v>56.044533333333327</v>
       </c>
       <c r="L16" s="1">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1">
-        <v>55.099999999999994</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.044533333333327</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -8234,13 +9057,18 @@
         <v>48.1173</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M17" s="1">
-        <v>46.199999999999996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>48.1173</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>167</v>
       </c>
@@ -8279,10 +9107,15 @@
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>38.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>38.19166666666667</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -8321,10 +9154,15 @@
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>66.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.008099999999999</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -8360,13 +9198,18 @@
         <v>57.995233333333331</v>
       </c>
       <c r="L20" s="1">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="M20" s="1">
-        <v>57.05</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57.995233333333331</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -8405,10 +9248,15 @@
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>62.449999999999996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.324816666666663</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>171</v>
       </c>
@@ -8444,13 +9292,18 @@
         <v>54.010216666666665</v>
       </c>
       <c r="L22" s="1">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="M22" s="1">
-        <v>53.349999999999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54.010216666666665</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -8486,13 +9339,18 @@
         <v>56.543500000000002</v>
       </c>
       <c r="L23" s="1">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="M23" s="1">
-        <v>64.099999999999994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.053333333333342</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>173</v>
       </c>
@@ -8528,13 +9386,18 @@
         <v>58.930583333333331</v>
       </c>
       <c r="L24" s="1">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="M24" s="1">
-        <v>60.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.851666666666667</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>174</v>
       </c>
@@ -8570,13 +9433,18 @@
         <v>57.394483333333326</v>
       </c>
       <c r="L25" s="1">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="M25" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.86</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>175</v>
       </c>
@@ -8612,13 +9480,18 @@
         <v>67.491299999999995</v>
       </c>
       <c r="L26" s="1">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="M26" s="1">
-        <v>74.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.53</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>176</v>
       </c>
@@ -8654,13 +9527,18 @@
         <v>60.25031666666667</v>
       </c>
       <c r="L27" s="1">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="M27" s="1">
-        <v>56.55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.25031666666667</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>177</v>
       </c>
@@ -8696,13 +9574,18 @@
         <v>46.34726666666667</v>
       </c>
       <c r="L28" s="1">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="M28" s="1">
-        <v>48.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>48.056666666666665</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>178</v>
       </c>
@@ -8738,13 +9621,18 @@
         <v>58.19404999999999</v>
       </c>
       <c r="L29" s="1">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="M29" s="1">
-        <v>66.599999999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.471666666666664</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>179</v>
       </c>
@@ -8783,10 +9671,15 @@
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>65.199999999999989</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.661466666666655</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>180</v>
       </c>
@@ -8822,13 +9715,18 @@
         <v>52.051666666666662</v>
       </c>
       <c r="L31" s="1">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="M31" s="1">
-        <v>55.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.084999999999994</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>181</v>
       </c>
@@ -8867,10 +9765,15 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>60.199999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.995366666666662</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>182</v>
       </c>
@@ -8906,13 +9809,18 @@
         <v>51.900233333333333</v>
       </c>
       <c r="L33" s="1">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="M33" s="1">
-        <v>55.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.213333333333331</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -8951,10 +9859,15 @@
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.709733333333332</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>184</v>
       </c>
@@ -8990,13 +9903,18 @@
         <v>49.809149999999988</v>
       </c>
       <c r="L35" s="1">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M35" s="1">
-        <v>47.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>49.809149999999988</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -9032,13 +9950,18 @@
         <v>54.130733333333332</v>
       </c>
       <c r="L36" s="1">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="M36" s="1">
-        <v>51.949999999999996</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54.130733333333332</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>186</v>
       </c>
@@ -9077,10 +10000,15 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>28.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>28.58583333333333</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -9119,10 +10047,15 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>65.599999999999994</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.248249999999999</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>188</v>
       </c>
@@ -9158,13 +10091,18 @@
         <v>55.738566666666664</v>
       </c>
       <c r="L39" s="1">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="M39" s="1">
-        <v>55.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.738566666666664</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>189</v>
       </c>
@@ -9203,10 +10141,15 @@
         <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>45.099999999999994</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>47.9315</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>190</v>
       </c>
@@ -9245,10 +10188,15 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>69.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.084983333333327</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -9284,13 +10232,18 @@
         <v>45.500733333333329</v>
       </c>
       <c r="L42" s="1">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="M42" s="1">
-        <v>56.199999999999996</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.106666666666662</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>192</v>
       </c>
@@ -9326,13 +10279,18 @@
         <v>56.800550000000001</v>
       </c>
       <c r="L43" s="1">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="M43" s="1">
-        <v>59.05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>58.991666666666667</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>193</v>
       </c>
@@ -9371,10 +10329,15 @@
         <v>0</v>
       </c>
       <c r="M44" s="1">
-        <v>27.499999999999996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>28.956233333333326</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -9410,13 +10373,18 @@
         <v>56.238099999999996</v>
       </c>
       <c r="L45" s="1">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="M45" s="1">
-        <v>62.899999999999991</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>63.063333333333325</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -9455,10 +10423,15 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>68.399999999999991</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>67.871733333333339</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -9497,10 +10470,15 @@
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>48.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>52.232499999999995</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -9536,13 +10514,18 @@
         <v>51.130166666666653</v>
       </c>
       <c r="L48" s="1">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="M48" s="1">
-        <v>49.399999999999991</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>51.130166666666668</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -9578,13 +10561,18 @@
         <v>45.789899999999989</v>
       </c>
       <c r="L49" s="1">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="M49" s="1">
-        <v>43.65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>45.789899999999989</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>199</v>
       </c>
@@ -9623,10 +10611,15 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50.569066666666657</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>200</v>
       </c>
@@ -9662,13 +10655,18 @@
         <v>74.679266666666649</v>
       </c>
       <c r="L51" s="1">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="M51" s="1">
-        <v>75.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>75.413333333333313</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -9677,6 +10675,10 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
+      <c r="N52">
+        <f>COUNTIF(N2:N51,"AP")</f>
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -9686,13 +10688,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A4A384-9885-48EF-9409-BDD8E2A0903E}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9732,8 +10734,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>201</v>
       </c>
@@ -9769,13 +10774,18 @@
         <v>76.579070073994998</v>
       </c>
       <c r="L2" s="1">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="M2" s="1">
-        <v>71.099999999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>76.579070073994998</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -9811,13 +10821,18 @@
         <v>63.404541254933328</v>
       </c>
       <c r="L3" s="1">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="M3" s="1">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M3:M49" si="1">(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>63.404541254933328</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N49" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>203</v>
       </c>
@@ -9856,10 +10871,15 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>61.749999999999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>61.52176262326666</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>204</v>
       </c>
@@ -9898,10 +10918,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>67.150000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.793837080889176</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>205</v>
       </c>
@@ -9940,10 +10965,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>9.3999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>9.3271999999999995</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>206</v>
       </c>
@@ -9979,13 +11009,18 @@
         <v>58.888716345459997</v>
       </c>
       <c r="L7" s="1">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1">
-        <v>58.05</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>58.888716345459997</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -10024,10 +11059,15 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>61.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.980756202403327</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>208</v>
       </c>
@@ -10066,10 +11106,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>51.149999999999991</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55.198283885298324</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -10108,10 +11153,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>62.599999999999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.26417829261333</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>210</v>
       </c>
@@ -10150,10 +11200,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>67.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.657683094203335</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>211</v>
       </c>
@@ -10192,10 +11247,15 @@
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.876748926398328</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>212</v>
       </c>
@@ -10234,10 +11294,15 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>60.599999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.462232564366666</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>213</v>
       </c>
@@ -10276,10 +11341,15 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>2.4499999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>2.4849999999999999</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>214</v>
       </c>
@@ -10318,10 +11388,15 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>60.449999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.955459864959998</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>215</v>
       </c>
@@ -10360,10 +11435,15 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>33.992139220133325</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>216</v>
       </c>
@@ -10399,13 +11479,18 @@
         <v>44.675791205949999</v>
       </c>
       <c r="L17" s="1">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="M17" s="1">
-        <v>46.099999999999994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>46.08745787261666</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>217</v>
       </c>
@@ -10444,10 +11529,15 @@
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>69.349999999999994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.06566391556666</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>218</v>
       </c>
@@ -10486,10 +11576,15 @@
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>74.349999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>74.169565471903326</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>219</v>
       </c>
@@ -10528,10 +11623,15 @@
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>14.799999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>14.942916666666665</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>220</v>
       </c>
@@ -10570,10 +11670,15 @@
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>67.650000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>67.034976895301668</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>221</v>
       </c>
@@ -10612,10 +11717,15 @@
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>73.649999999999991</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>73.195284515991673</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>222</v>
       </c>
@@ -10654,10 +11764,15 @@
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>64.599999999999994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.513571778680003</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -10693,13 +11808,18 @@
         <v>53.75608715705166</v>
       </c>
       <c r="L24" s="1">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="M24" s="1">
-        <v>52.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.75608715705166</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>224</v>
       </c>
@@ -10738,10 +11858,15 @@
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>70.349999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.141581969678327</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>225</v>
       </c>
@@ -10777,13 +11902,18 @@
         <v>58.083308225068336</v>
       </c>
       <c r="L26" s="1">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="M26" s="1">
-        <v>62.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.662499999999994</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>226</v>
       </c>
@@ -10822,10 +11952,15 @@
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>67.199999999999989</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.747009125708331</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>227</v>
       </c>
@@ -10864,10 +11999,15 @@
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>42.699999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>71.259889265369992</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>228</v>
       </c>
@@ -10903,13 +12043,18 @@
         <v>50.197038947773336</v>
       </c>
       <c r="L29" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="M29" s="1">
-        <v>46.099999999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50.197038947773336</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>229</v>
       </c>
@@ -10945,13 +12090,18 @@
         <v>73.072197889269987</v>
       </c>
       <c r="L30" s="1">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="M30" s="1">
-        <v>70.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>73.072197889269987</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>230</v>
       </c>
@@ -10990,10 +12140,15 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>60.699999999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.097547415688325</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>231</v>
       </c>
@@ -11032,10 +12187,15 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>83.48595029668833</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>232</v>
       </c>
@@ -11071,13 +12231,18 @@
         <v>70.633730350995833</v>
       </c>
       <c r="L33" s="1">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="M33" s="1">
-        <v>68.150000000000006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.633730350995833</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>233</v>
       </c>
@@ -11116,10 +12281,15 @@
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>76.650000000000006</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>76.30224899289999</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>234</v>
       </c>
@@ -11155,13 +12325,18 @@
         <v>56.827339674368325</v>
       </c>
       <c r="L35" s="1">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="M35" s="1">
-        <v>55.199999999999996</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.827339674368325</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -11200,10 +12375,15 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>61.199999999999996</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.888489267786667</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>236</v>
       </c>
@@ -11242,10 +12422,15 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>64.399999999999991</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.088011996878336</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>237</v>
       </c>
@@ -11284,10 +12469,15 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>74.530655321306668</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>238</v>
       </c>
@@ -11323,13 +12513,18 @@
         <v>58.706249999999997</v>
       </c>
       <c r="L39" s="1">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="M39" s="1">
-        <v>59.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59.826249999999995</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -11365,13 +12560,18 @@
         <v>54.62211277243</v>
       </c>
       <c r="L40" s="1">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="M40" s="1">
-        <v>52.849999999999994</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54.62211277243</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -11407,13 +12607,18 @@
         <v>54.290859018428328</v>
       </c>
       <c r="L41" s="1">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="M41" s="1">
-        <v>54.849999999999994</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54.91396921762</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>241</v>
       </c>
@@ -11452,10 +12657,15 @@
         <v>0</v>
       </c>
       <c r="M42" s="1">
-        <v>69.099999999999994</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.774214628549998</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>242</v>
       </c>
@@ -11494,10 +12704,15 @@
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>46.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.513940814110001</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>243</v>
       </c>
@@ -11533,13 +12748,18 @@
         <v>57.741432120989998</v>
       </c>
       <c r="L44" s="1">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="M44" s="1">
-        <v>57.65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57.741432120989991</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>244</v>
       </c>
@@ -11575,13 +12795,18 @@
         <v>52.316441059088334</v>
       </c>
       <c r="L45" s="1">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="M45" s="1">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.930000000000007</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>245</v>
       </c>
@@ -11620,10 +12845,15 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>70.849999999999994</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.348171025406657</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>246</v>
       </c>
@@ -11662,10 +12892,15 @@
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>46.849999999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.123703068056663</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -11704,10 +12939,15 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>62.449999999999996</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.109005669878329</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>248</v>
       </c>
@@ -11746,10 +12986,15 @@
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>14.599999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>14.701216419733329</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -11758,8 +13003,12 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N50">
+        <f>COUNTIF(N2:N49,"AP")</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -11769,7 +13018,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -11787,13 +13036,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4309DD8B-C3AE-490A-BFD6-B77DAC7DA4EB}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11833,8 +13082,11 @@
       <c r="M1" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>249</v>
       </c>
@@ -11873,10 +13125,15 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>69.849999999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <v>69.471296454184994</v>
+      </c>
+      <c r="N2" t="str">
+        <f>IF(M2&gt;59.5,"AP","RP")</f>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>250</v>
       </c>
@@ -11915,10 +13172,15 @@
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>41.05</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M3:M49" si="1">(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <v>44.614382153079994</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N49" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>251</v>
       </c>
@@ -11957,10 +13219,15 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>63.55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>63.298644614179992</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>252</v>
       </c>
@@ -11999,10 +13266,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>63.999999999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>63.455141060433327</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>253</v>
       </c>
@@ -12041,10 +13313,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>67.45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.846465981768333</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>254</v>
       </c>
@@ -12083,10 +13360,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>61.849999999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>61.747031504999995</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>255</v>
       </c>
@@ -12125,10 +13407,15 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>73.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>73.407575338726659</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>256</v>
       </c>
@@ -12167,10 +13454,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>72.599999999999994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>72.489166666666662</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -12206,13 +13498,18 @@
         <v>53.131503680999998</v>
       </c>
       <c r="L10" s="1">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="M10" s="1">
-        <v>53.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>53.131503680999998</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -12251,10 +13548,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>84.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>84.431739069226666</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -12290,13 +13592,18 @@
         <v>56.893700434426663</v>
       </c>
       <c r="L12" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M12" s="1">
-        <v>51.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.893700434426663</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>260</v>
       </c>
@@ -12335,10 +13642,15 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>76.949999999999989</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>76.665935129108334</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>261</v>
       </c>
@@ -12377,10 +13689,15 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>76.399999999999991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>75.915630239439992</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -12419,10 +13736,15 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>60.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.039999999999992</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -12461,10 +13783,15 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>45.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50.26422162980667</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>264</v>
       </c>
@@ -12500,13 +13827,18 @@
         <v>61.42795485705733</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M17" s="1">
-        <v>60.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>61.42795485705733</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -12545,10 +13877,15 @@
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>48.349999999999994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>52.59426095968</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -12587,10 +13924,15 @@
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>46.527383333333333</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -12629,10 +13971,15 @@
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>77.399478588846648</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -12671,10 +14018,15 @@
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>74.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>74.083333333333329</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>269</v>
       </c>
@@ -12713,10 +14065,15 @@
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>62.949999999999989</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.898559555489996</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -12755,10 +14112,15 @@
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>68.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>68.382735392698336</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>271</v>
       </c>
@@ -12797,10 +14159,15 @@
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <v>64.099999999999994</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>63.771232847416655</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -12836,13 +14203,18 @@
         <v>57.987718325576665</v>
       </c>
       <c r="L25" s="1">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M25" s="1">
-        <v>58.099999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57.987718325576665</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -12881,10 +14253,15 @@
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>69.150000000000006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.021035989673322</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -12923,10 +14300,15 @@
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>69.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.1273022524</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -12965,10 +14347,15 @@
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>67.46846563799933</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -13007,10 +14394,15 @@
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>62.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62.031331927883329</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -13049,10 +14441,15 @@
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>65.399999999999991</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.961596857549992</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -13091,10 +14488,15 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>39.199999999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>39.211666666666666</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -13133,10 +14535,15 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>67.099999999999994</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66.665020470656657</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>280</v>
       </c>
@@ -13175,10 +14582,15 @@
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <v>39.450000000000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>39.18532478978333</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>281</v>
       </c>
@@ -13214,13 +14626,18 @@
         <v>58.024634274013323</v>
       </c>
       <c r="L34" s="1">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="M34" s="1">
-        <v>60.599999999999994</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>60.48109794171333</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -13259,10 +14676,15 @@
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>65.199999999999989</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>64.787983109516659</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -13301,10 +14723,15 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>63.310324086268338</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>284</v>
       </c>
@@ -13343,10 +14770,15 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>32.347499999999997</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>285</v>
       </c>
@@ -13385,10 +14817,15 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>70.55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>70.296250000000001</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>286</v>
       </c>
@@ -13424,13 +14861,18 @@
         <v>54.822018460479995</v>
       </c>
       <c r="L39" s="1">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="M39" s="1">
-        <v>53.65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54.822018460479995</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -13466,13 +14908,18 @@
         <v>65.835949999999997</v>
       </c>
       <c r="L40" s="1">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="M40" s="1">
-        <v>63.099999999999994</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>65.835949999999997</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>288</v>
       </c>
@@ -13511,10 +14958,15 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>47.699999999999996</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>51.036022746279997</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>289</v>
       </c>
@@ -13550,13 +15002,18 @@
         <v>55.60833011199999</v>
       </c>
       <c r="L42" s="1">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="M42" s="1">
-        <v>56.649999999999991</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>56.710830111999996</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>290</v>
       </c>
@@ -13595,10 +15052,15 @@
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>70.149999999999991</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>69.943669462813332</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -13637,10 +15099,15 @@
         <v>0</v>
       </c>
       <c r="M44" s="1">
-        <v>45.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>51.926743758501658</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>292</v>
       </c>
@@ -13679,10 +15146,15 @@
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <v>74.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>74.315787171233339</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -13718,13 +15190,18 @@
         <v>83.584363750816664</v>
       </c>
       <c r="L46" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M46" s="1">
-        <v>82.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>83.584363750816664</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>AP</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -13763,10 +15240,15 @@
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>27.449999999999996</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>28.742387461924999</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>295</v>
       </c>
@@ -13805,10 +15287,15 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>37.700000000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>37.732315025376664</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -13844,13 +15331,18 @@
         <v>58.365339994759992</v>
       </c>
       <c r="L49" s="1">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="M49" s="1">
-        <v>58.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>58.365339994759992</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>RP</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -13859,8 +15351,12 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N50">
+        <f>COUNTIF(N2:N49,"AP")</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -13870,7 +15366,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>

--- a/CoursesList/Grades_PAO_II_2025_FEM.xlsx
+++ b/CoursesList/Grades_PAO_II_2025_FEM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisp\Desktop\Papers\J4 Tutor Socratico\Notas PAO II 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339836EB-9999-4BEC-9E1B-6E9DD3B43F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2180B021-AEF9-4E19-AF39-7AE5D953A4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{32ECD927-A2E7-4219-8E68-D6FC45AD5483}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="301">
   <si>
     <t>codigo</t>
   </si>
@@ -924,9 +924,6 @@
   </si>
   <si>
     <t>FINAL</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
   <si>
     <t>tercer examen</t>
@@ -998,30 +995,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1331,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6683928A-C7F0-4796-BECC-A9961919393E}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -1372,13 +1346,13 @@
         <v>297</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -1471,7 +1445,7 @@
         <v>14.797516666666667</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N53" si="2">IF(M3&gt;59.5,"AP","RP")</f>
+        <f t="shared" ref="N3:N52" si="2">IF(M3&gt;59.5,"AP","RP")</f>
         <v>RP</v>
       </c>
     </row>
@@ -3776,12 +3750,6 @@
       <c r="N52" t="str">
         <f t="shared" si="2"/>
         <v>AP</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N53">
-        <f>COUNTIF(N2:N52,"AP")</f>
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3833,13 +3801,13 @@
         <v>297</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3881,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <f>(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
+        <f t="shared" ref="M2:M43" si="0">(0.7*(SUM(E2,I2,L2)-MIN(E2,I2,L2))/2)+(0.3*J2)</f>
         <v>44.880566666666667</v>
       </c>
       <c r="N2" t="str">
@@ -3921,18 +3889,18 @@
         <v>46</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K43" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <f t="shared" ref="K3:K43" si="1">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>61.242033333333325</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <f>(0.7*(SUM(E3,I3,L3)-MIN(E3,I3,L3))/2)+(0.3*J3)</f>
+        <f t="shared" si="0"/>
         <v>61.242033333333325</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N43" si="1">IF(M3&gt;59.5,"AP","RP")</f>
+        <f t="shared" ref="N3:N43" si="2">IF(M3&gt;59.5,"AP","RP")</f>
         <v>AP</v>
       </c>
     </row>
@@ -3968,18 +3936,18 @@
         <v>9</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.52923333333333</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <f>(0.7*(SUM(E4,I4,L4)-MIN(E4,I4,L4))/2)+(0.3*J4)</f>
+        <f t="shared" si="0"/>
         <v>20.52923333333333</v>
       </c>
       <c r="N4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4015,18 +3983,18 @@
         <v>50</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49.736566666666661</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <f>(0.7*(SUM(E5,I5,L5)-MIN(E5,I5,L5))/2)+(0.3*J5)</f>
+        <f t="shared" si="0"/>
         <v>49.736566666666661</v>
       </c>
       <c r="N5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4062,18 +4030,18 @@
         <v>12</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19.464799999999997</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <f>(0.7*(SUM(E6,I6,L6)-MIN(E6,I6,L6))/2)+(0.3*J6)</f>
+        <f t="shared" si="0"/>
         <v>19.464799999999997</v>
       </c>
       <c r="N6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4109,18 +4077,18 @@
         <v>51</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.197399999999995</v>
       </c>
       <c r="L7" s="1">
         <v>48</v>
       </c>
       <c r="M7" s="1">
-        <f>(0.7*(SUM(E7,I7,L7)-MIN(E7,I7,L7))/2)+(0.3*J7)</f>
+        <f t="shared" si="0"/>
         <v>51.98</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4156,18 +4124,18 @@
         <v>48</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37.052933333333328</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <f>(0.7*(SUM(E8,I8,L8)-MIN(E8,I8,L8))/2)+(0.3*J8)</f>
+        <f t="shared" si="0"/>
         <v>37.052933333333328</v>
       </c>
       <c r="N8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4203,18 +4171,18 @@
         <v>68</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64.725166666666667</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f>(0.7*(SUM(E9,I9,L9)-MIN(E9,I9,L9))/2)+(0.3*J9)</f>
+        <f t="shared" si="0"/>
         <v>64.725166666666667</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -4250,18 +4218,18 @@
         <v>57</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62.599999999999994</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <f>(0.7*(SUM(E10,I10,L10)-MIN(E10,I10,L10))/2)+(0.3*J10)</f>
+        <f t="shared" si="0"/>
         <v>62.599999999999994</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -4297,18 +4265,18 @@
         <v>6</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.870066666666666</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <f>(0.7*(SUM(E11,I11,L11)-MIN(E11,I11,L11))/2)+(0.3*J11)</f>
+        <f t="shared" si="0"/>
         <v>16.870066666666666</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4344,18 +4312,18 @@
         <v>21</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46.525733333333328</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <f>(0.7*(SUM(E12,I12,L12)-MIN(E12,I12,L12))/2)+(0.3*J12)</f>
+        <f t="shared" si="0"/>
         <v>46.525733333333328</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4391,18 +4359,18 @@
         <v>48</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.27806666666666</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <f>(0.7*(SUM(E13,I13,L13)-MIN(E13,I13,L13))/2)+(0.3*J13)</f>
+        <f t="shared" si="0"/>
         <v>61.27806666666666</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -4438,18 +4406,18 @@
         <v>18</v>
       </c>
       <c r="K14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.993099999999998</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <f>(0.7*(SUM(E14,I14,L14)-MIN(E14,I14,L14))/2)+(0.3*J14)</f>
+        <f t="shared" si="0"/>
         <v>29.993099999999998</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4485,18 +4453,18 @@
         <v>25</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26.971666666666664</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <f>(0.7*(SUM(E15,I15,L15)-MIN(E15,I15,L15))/2)+(0.3*J15)</f>
+        <f t="shared" si="0"/>
         <v>26.971666666666664</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4532,18 +4500,18 @@
         <v>86</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65.513333333333335</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <f>(0.7*(SUM(E16,I16,L16)-MIN(E16,I16,L16))/2)+(0.3*J16)</f>
+        <f t="shared" si="0"/>
         <v>65.513333333333335</v>
       </c>
       <c r="N16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -4579,18 +4547,18 @@
         <v>26</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35.58626666666666</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f>(0.7*(SUM(E17,I17,L17)-MIN(E17,I17,L17))/2)+(0.3*J17)</f>
+        <f t="shared" si="0"/>
         <v>35.58626666666666</v>
       </c>
       <c r="N17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4626,18 +4594,18 @@
         <v>45</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48.214866666666666</v>
       </c>
       <c r="L18" s="1">
         <v>50</v>
       </c>
       <c r="M18" s="1">
-        <f>(0.7*(SUM(E18,I18,L18)-MIN(E18,I18,L18))/2)+(0.3*J18)</f>
+        <f t="shared" si="0"/>
         <v>48.38986666666667</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4673,18 +4641,18 @@
         <v>32</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46.357933333333328</v>
       </c>
       <c r="L19" s="1">
         <v>49</v>
       </c>
       <c r="M19" s="1">
-        <f>(0.7*(SUM(E19,I19,L19)-MIN(E19,I19,L19))/2)+(0.3*J19)</f>
+        <f t="shared" si="0"/>
         <v>46.357933333333328</v>
       </c>
       <c r="N19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4720,18 +4688,18 @@
         <v>57</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>69.188866666666655</v>
       </c>
       <c r="L20" s="1">
         <v>61</v>
       </c>
       <c r="M20" s="1">
-        <f>(0.7*(SUM(E20,I20,L20)-MIN(E20,I20,L20))/2)+(0.3*J20)</f>
+        <f t="shared" si="0"/>
         <v>69.188866666666655</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -4767,18 +4735,18 @@
         <v>43</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50.450916666666657</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <f>(0.7*(SUM(E21,I21,L21)-MIN(E21,I21,L21))/2)+(0.3*J21)</f>
+        <f t="shared" si="0"/>
         <v>50.450916666666657</v>
       </c>
       <c r="N21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4814,18 +4782,18 @@
         <v>47</v>
       </c>
       <c r="K22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.700150000000001</v>
       </c>
       <c r="L22" s="1">
         <v>44</v>
       </c>
       <c r="M22" s="1">
-        <f>(0.7*(SUM(E22,I22,L22)-MIN(E22,I22,L22))/2)+(0.3*J22)</f>
+        <f t="shared" si="0"/>
         <v>51.700150000000001</v>
       </c>
       <c r="N22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4861,18 +4829,18 @@
         <v>28</v>
       </c>
       <c r="K23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48.577666666666659</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f>(0.7*(SUM(E23,I23,L23)-MIN(E23,I23,L23))/2)+(0.3*J23)</f>
+        <f t="shared" si="0"/>
         <v>48.577666666666659</v>
       </c>
       <c r="N23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4908,18 +4876,18 @@
         <v>32</v>
       </c>
       <c r="K24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46.633266666666664</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>(0.7*(SUM(E24,I24,L24)-MIN(E24,I24,L24))/2)+(0.3*J24)</f>
+        <f t="shared" si="0"/>
         <v>46.633266666666664</v>
       </c>
       <c r="N24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -4955,18 +4923,18 @@
         <v>38</v>
       </c>
       <c r="K25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47.198116666666664</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <f>(0.7*(SUM(E25,I25,L25)-MIN(E25,I25,L25))/2)+(0.3*J25)</f>
+        <f t="shared" si="0"/>
         <v>47.198116666666664</v>
       </c>
       <c r="N25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5002,18 +4970,18 @@
         <v>13</v>
       </c>
       <c r="K26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23.894333333333329</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <f>(0.7*(SUM(E26,I26,L26)-MIN(E26,I26,L26))/2)+(0.3*J26)</f>
+        <f t="shared" si="0"/>
         <v>23.894333333333329</v>
       </c>
       <c r="N26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5049,18 +5017,18 @@
         <v>6</v>
       </c>
       <c r="K27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.581466666666664</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <f>(0.7*(SUM(E27,I27,L27)-MIN(E27,I27,L27))/2)+(0.3*J27)</f>
+        <f t="shared" si="0"/>
         <v>13.581466666666664</v>
       </c>
       <c r="N27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5096,18 +5064,18 @@
         <v>19</v>
       </c>
       <c r="K28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25.754766666666665</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <f>(0.7*(SUM(E28,I28,L28)-MIN(E28,I28,L28))/2)+(0.3*J28)</f>
+        <f t="shared" si="0"/>
         <v>25.754766666666665</v>
       </c>
       <c r="N28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5143,18 +5111,18 @@
         <v>51</v>
       </c>
       <c r="K29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59.532066666666658</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <f>(0.7*(SUM(E29,I29,L29)-MIN(E29,I29,L29))/2)+(0.3*J29)</f>
+        <f t="shared" si="0"/>
         <v>59.532066666666658</v>
       </c>
       <c r="N29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5190,18 +5158,18 @@
         <v>51</v>
       </c>
       <c r="K30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59.80436666666666</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <f>(0.7*(SUM(E30,I30,L30)-MIN(E30,I30,L30))/2)+(0.3*J30)</f>
+        <f t="shared" si="0"/>
         <v>59.80436666666666</v>
       </c>
       <c r="N30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5237,18 +5205,18 @@
         <v>30</v>
       </c>
       <c r="K31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42.542833333333334</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <f>(0.7*(SUM(E31,I31,L31)-MIN(E31,I31,L31))/2)+(0.3*J31)</f>
+        <f t="shared" si="0"/>
         <v>42.542833333333334</v>
       </c>
       <c r="N31" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5284,18 +5252,18 @@
         <v>63</v>
       </c>
       <c r="K32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59.60126666666666</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <f>(0.7*(SUM(E32,I32,L32)-MIN(E32,I32,L32))/2)+(0.3*J32)</f>
+        <f t="shared" si="0"/>
         <v>59.60126666666666</v>
       </c>
       <c r="N32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5331,18 +5299,18 @@
         <v>29</v>
       </c>
       <c r="K33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49.428333333333327</v>
       </c>
       <c r="L33" s="1">
         <v>56</v>
       </c>
       <c r="M33" s="1">
-        <f>(0.7*(SUM(E33,I33,L33)-MIN(E33,I33,L33))/2)+(0.3*J33)</f>
+        <f t="shared" si="0"/>
         <v>49.510000000000005</v>
       </c>
       <c r="N33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5378,18 +5346,18 @@
         <v>46</v>
       </c>
       <c r="K34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56.29</v>
       </c>
       <c r="L34" s="1">
         <v>75</v>
       </c>
       <c r="M34" s="1">
-        <f>(0.7*(SUM(E34,I34,L34)-MIN(E34,I34,L34))/2)+(0.3*J34)</f>
+        <f t="shared" si="0"/>
         <v>63.604999999999997</v>
       </c>
       <c r="N34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5425,18 +5393,18 @@
         <v>21</v>
       </c>
       <c r="K35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37.134999999999998</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <f>(0.7*(SUM(E35,I35,L35)-MIN(E35,I35,L35))/2)+(0.3*J35)</f>
+        <f t="shared" si="0"/>
         <v>37.134999999999998</v>
       </c>
       <c r="N35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5472,18 +5440,18 @@
         <v>40</v>
       </c>
       <c r="K36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55.454716666666663</v>
       </c>
       <c r="L36" s="1">
         <v>58</v>
       </c>
       <c r="M36" s="1">
-        <f>(0.7*(SUM(E36,I36,L36)-MIN(E36,I36,L36))/2)+(0.3*J36)</f>
+        <f t="shared" si="0"/>
         <v>55.45471666666667</v>
       </c>
       <c r="N36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5519,18 +5487,18 @@
         <v>30</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43.522133333333336</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <f>(0.7*(SUM(E37,I37,L37)-MIN(E37,I37,L37))/2)+(0.3*J37)</f>
+        <f t="shared" si="0"/>
         <v>43.522133333333336</v>
       </c>
       <c r="N37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5566,18 +5534,18 @@
         <v>25</v>
       </c>
       <c r="K38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31.352266666666665</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <f>(0.7*(SUM(E38,I38,L38)-MIN(E38,I38,L38))/2)+(0.3*J38)</f>
+        <f t="shared" si="0"/>
         <v>31.352266666666665</v>
       </c>
       <c r="N38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5613,18 +5581,18 @@
         <v>0</v>
       </c>
       <c r="K39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.948333333333333</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <f>(0.7*(SUM(E39,I39,L39)-MIN(E39,I39,L39))/2)+(0.3*J39)</f>
+        <f t="shared" si="0"/>
         <v>1.948333333333333</v>
       </c>
       <c r="N39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5660,18 +5628,18 @@
         <v>91</v>
       </c>
       <c r="K40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>67.214233333333326</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
       </c>
       <c r="M40" s="1">
-        <f>(0.7*(SUM(E40,I40,L40)-MIN(E40,I40,L40))/2)+(0.3*J40)</f>
+        <f t="shared" si="0"/>
         <v>67.214233333333326</v>
       </c>
       <c r="N40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5707,18 +5675,18 @@
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4033333333333333</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f>(0.7*(SUM(E41,I41,L41)-MIN(E41,I41,L41))/2)+(0.3*J41)</f>
+        <f t="shared" si="0"/>
         <v>2.4033333333333333</v>
       </c>
       <c r="N41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5754,18 +5722,18 @@
         <v>61</v>
       </c>
       <c r="K42" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60.004599999999996</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
       </c>
       <c r="M42" s="1">
-        <f>(0.7*(SUM(E42,I42,L42)-MIN(E42,I42,L42))/2)+(0.3*J42)</f>
+        <f t="shared" si="0"/>
         <v>60.004599999999996</v>
       </c>
       <c r="N42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AP</v>
       </c>
     </row>
@@ -5801,18 +5769,18 @@
         <v>48</v>
       </c>
       <c r="K43" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43.982933333333328</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <f>(0.7*(SUM(E43,I43,L43)-MIN(E43,I43,L43))/2)+(0.3*J43)</f>
+        <f t="shared" si="0"/>
         <v>43.982933333333328</v>
       </c>
       <c r="N43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>RP</v>
       </c>
     </row>
@@ -5825,10 +5793,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="N44" s="3">
-        <f>COUNTIF(N2:N43,"AP")</f>
-        <v>12</v>
-      </c>
+      <c r="N44" s="3"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
@@ -5956,16 +5921,16 @@
         <v>60</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -8233,10 +8198,6 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="N50">
-        <f>COUNTIF(N2:N49,"AP")</f>
-        <v>10</v>
-      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
@@ -8304,16 +8265,16 @@
         <v>60</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -8395,7 +8356,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:M51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
+        <f t="shared" ref="K3:K51" si="0">(0.3*J3)+((E3+I3)*0.35)</f>
         <v>66.032466666666664</v>
       </c>
       <c r="L3" s="1">
@@ -10675,10 +10636,6 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="N52">
-        <f>COUNTIF(N2:N51,"AP")</f>
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -10726,16 +10683,16 @@
         <v>60</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -13003,10 +12960,6 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="N50">
-        <f>COUNTIF(N2:N49,"AP")</f>
-        <v>31</v>
-      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
@@ -13074,16 +13027,16 @@
         <v>60</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -15351,10 +15304,6 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="N50">
-        <f>COUNTIF(N2:N49,"AP")</f>
-        <v>31</v>
-      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
